--- a/CLI/download_report.xlsx
+++ b/CLI/download_report.xlsx
@@ -448,15 +448,15 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.tescoplc.com/media/u1wlq2qf/tesco-plc-annual-report-2023.pdf'</t>
+          <t>403, message='Forbidden', url='https://media.defense.gov/2024/Dec/18/2003615520/-1/-1/0/MILITARY-AND-SECURITY-DEVELOPMENTS-INVOLVING-THE-PEOPLES-REPUBLIC-OF-CHINA-2024.PDF'</t>
         </is>
       </c>
     </row>
@@ -465,66 +465,66 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cannot connect to host uploads.vw-mms.de:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+          <t>404, message='Not Found', url='https://pka.dk/globalassets/4-this-is-pka/annual-report/2023/annual-report-2023-pka-pension.pdf'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>116</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>271</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>271_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
+        </is>
+      </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.statestreet.com/web/about/our-story/annual-report/documents/ssc-annual-report-2024.pdf'</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>156</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>156_Annual%20Report%202021.pdf</t>
-        </is>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="b">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.bls.gov/news.release/pdf/cpi.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="b">
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://investor.gm.com/static-files/1fff6f59-551f-4fe0-bca9-74bfc9a56aeb'</t>
+          <t>404, message='Not Found', url='https://www.statestreet.com/web/about/our-story/annual-report/documents/ssc-annual-report-2024.pdf'</t>
         </is>
       </c>
     </row>
@@ -533,15 +533,15 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.dni.gov/files/ODNI/documents/assessments/ATA-2025-Unclassified-Report.pdf'</t>
+          <t>Cannot connect to host uploads.vw-mms.de:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
         </is>
       </c>
     </row>
@@ -550,79 +550,79 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://investor-en.tcmgroup.dk/system/files-encrypted/nasdaq_kms/assets/2024/03/13/9-54-17/Annual%20report%202023.pdf'</t>
+          <t>Secondary URL is not a valid PDF.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>194</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>194_Tusla_-_Annual_Report_and_Financial_Statements_2023.pdf</t>
-        </is>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="b">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.dni.gov/files/ODNI/documents/assessments/ATA-2025-Unclassified-Report.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>253_BUP%20Annual%20Report%202024.pdf</t>
-        </is>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://investor.gm.com/static-files/1fff6f59-551f-4fe0-bca9-74bfc9a56aeb'</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>39_FINAL_Annual_Report_2023.pdf</t>
-        </is>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="b">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.tescoplc.com/media/u1wlq2qf/tesco-plc-annual-report-2023.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="b">
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2_danske-bank---annual-report-2024.pdf</t>
+          <t>76_eurofins-scientific-2024-annual-report.pdf</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -635,15 +635,15 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>38_NMG2015AnnualReport.pdf</t>
+          <t>2_danske-bank---annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
@@ -652,11 +652,11 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>137_2024-Annual-Report.pdf</t>
+          <t>37_grantthornton_annual-report_2023_uk.pdf</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -666,31 +666,31 @@
     </row>
     <row r="15">
       <c r="A15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>196</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>57_annual-report-2024.pdf</t>
+        </is>
+      </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.sampension.dk/media/cce8d8d6-4bd0-4483-a862-c92c6cb7154c/zPZytg/PDF%20dokumenter/%C3%85rsrapporter/Annual%20report%202023%20SP.pdf'</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="b">
         <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>118_annual_report_2023.pdf</t>
+          <t>194_Tusla_-_Annual_Report_and_Financial_Statements_2023.pdf</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -703,11 +703,11 @@
         <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>233</v>
+        <v>38</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>233_GLEN-2023-Annual-Report.pdf</t>
+          <t>38_NMG2015AnnualReport.pdf</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -717,35 +717,35 @@
     </row>
     <row r="18">
       <c r="A18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>60</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>156</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>156_Annual%20Report%202021.pdf</t>
+        </is>
+      </c>
       <c r="D18" t="b">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.infosys.com/investors/reports-filings/annual-report/annual/documents/infosys-ar-25.pdf'</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="b">
         <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>157</v>
+        <v>232</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>157_Inditex_Group_Annual_Accounts_2023.pdf</t>
+          <t>232_OSHA-RK-Forms-Package.pdf</t>
         </is>
       </c>
       <c r="D19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
@@ -754,11 +754,11 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>117</v>
+        <v>253</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>117_2023-annual-report.pdf</t>
+          <t>253_BUP%20Annual%20Report%202024.pdf</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -771,11 +771,11 @@
         <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>40_novo-holdings-2023-performance-report.pdf</t>
+          <t>117_2023-annual-report.pdf</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -785,31 +785,31 @@
     </row>
     <row r="22">
       <c r="A22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>20_relx-2024-annual-report.pdf</t>
-        </is>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="b">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://investor-en.tcmgroup.dk/system/files-encrypted/nasdaq_kms/assets/2024/03/13/9-54-17/Annual%20report%202023.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="b">
         <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>216_IAP-Annual-Report-2024-2025-EN.pdf</t>
+          <t>115_aarsregnskab_2019_engelsk_2020_ok.pdf</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -822,11 +822,11 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>138_mondi-group-integrated-report-and-financial-statements-2023.pdf</t>
+          <t>39_FINAL_Annual_Report_2023.pdf</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -839,15 +839,15 @@
         <v>1</v>
       </c>
       <c r="B25" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>97_kerry-group-annual-report-2024.pdf</t>
+          <t>137_2024-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr"/>
     </row>
@@ -856,11 +856,11 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>59_annualreports-2021_en.pdf</t>
+          <t>20_relx-2024-annual-report.pdf</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -870,31 +870,31 @@
     </row>
     <row r="27">
       <c r="A27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>119</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>195</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>195_Beiersdorf-annual-report-2023-en.pdf</t>
+        </is>
+      </c>
       <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.eif.org/files/records/eif-annual-report-2023.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="b">
         <v>1</v>
       </c>
       <c r="B28" t="n">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>77_Annual%20report%202024.pdf</t>
+          <t>176_CIRO-Annual-Report-2024-2025-EN.pdf</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -907,45 +907,45 @@
         <v>1</v>
       </c>
       <c r="B29" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>41_2023-03-02_gubra-annual_report_2022_final.pdf</t>
+          <t>79_Annual-Report-2024.pdf</t>
         </is>
       </c>
       <c r="D29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" t="n">
-        <v>80</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>80_MM_Annual_Report_2024.pdf</t>
-        </is>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.sampension.dk/media/cce8d8d6-4bd0-4483-a862-c92c6cb7154c/zPZytg/PDF%20dokumenter/%C3%85rsrapporter/Annual%20report%202023%20SP.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="b">
         <v>1</v>
       </c>
       <c r="B31" t="n">
-        <v>235</v>
+        <v>174</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>235_dk-KPMG-annual-report-2021.pdf</t>
+          <t>174_Bank-of-Ghana-2023-Annual-Report-and-Financial-Statements.pdf</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -955,52 +955,52 @@
     </row>
     <row r="32">
       <c r="A32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" t="n">
-        <v>100</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>40_novo-holdings-2023-performance-report.pdf</t>
+        </is>
+      </c>
       <c r="D32" t="b">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://pka.dk/globalassets/4-this-is-pka/annual-report/2023/annual-report-2023-pharmaconomists.pdf'</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B33" t="n">
-        <v>236</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>236_IPCC_AR6_SYR_LongerReport.pdf</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="b">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.infosys.com/investors/reports-filings/annual-report/annual/documents/infosys-ar-25.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="b">
         <v>1</v>
       </c>
       <c r="B34" t="n">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>255_calls_to_action_english2.pdf</t>
+          <t>1_novo-nordisk-annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr"/>
     </row>
@@ -1009,11 +1009,11 @@
         <v>1</v>
       </c>
       <c r="B35" t="n">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>217_via-annual-report-2021-EN.pdf</t>
+          <t>234_echapter.pdf</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -1026,11 +1026,11 @@
         <v>1</v>
       </c>
       <c r="B36" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>139_aig-2023-annual-report.pdf</t>
+          <t>96_ecit-annual-report-2023-62971.pdf</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -1040,35 +1040,35 @@
     </row>
     <row r="37">
       <c r="A37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>216_IAP-Annual-Report-2024-2025-EN.pdf</t>
+        </is>
+      </c>
       <c r="D37" t="b">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.cbs.dk:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="b">
         <v>1</v>
       </c>
       <c r="B38" t="n">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>256_i990.pdf</t>
+          <t>233_GLEN-2023-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr"/>
     </row>
@@ -1077,45 +1077,45 @@
         <v>1</v>
       </c>
       <c r="B39" t="n">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>197_WEF_Future_of_Jobs_Report_2025.pdf</t>
+          <t>235_dk-KPMG-annual-report-2021.pdf</t>
         </is>
       </c>
       <c r="D39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="n">
-        <v>120</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>97_kerry-group-annual-report-2024.pdf</t>
+        </is>
+      </c>
       <c r="D40" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.pwc.com/jm/en/research-publications/pdf/basic-understanding-of-a-companys-financials.pdf'</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="b">
         <v>1</v>
       </c>
       <c r="B41" t="n">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>61_loreal2024annualreport.pdf</t>
+          <t>118_annual_report_2023.pdf</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -1125,52 +1125,52 @@
     </row>
     <row r="42">
       <c r="A42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B42" t="n">
-        <v>79</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>79_Annual-Report-2024.pdf</t>
-        </is>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.eif.org/files/records/eif-annual-report-2023.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" t="n">
-        <v>198</v>
-      </c>
-      <c r="C43" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>80_MM_Annual_Report_2024.pdf</t>
+        </is>
+      </c>
       <c r="D43" t="b">
         <v>0</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.nato.int/nato_static_fl2014/assets/pdf/2024/3/pdf/sgar23-en.pdf'</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="b">
         <v>1</v>
       </c>
       <c r="B44" t="n">
-        <v>195</v>
+        <v>41</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>195_Beiersdorf-annual-report-2023-en.pdf</t>
+          <t>41_2023-03-02_gubra-annual_report_2022_final.pdf</t>
         </is>
       </c>
       <c r="D44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr"/>
     </row>
@@ -1179,11 +1179,11 @@
         <v>1</v>
       </c>
       <c r="B45" t="n">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>159_annual-report-2023-24.pdf</t>
+          <t>255_calls_to_action_english2.pdf</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -1193,31 +1193,31 @@
     </row>
     <row r="46">
       <c r="A46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1_novo-nordisk-annual-report-2024.pdf</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://pka.dk/globalassets/4-this-is-pka/annual-report/2023/annual-report-2023-pharmaconomists.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="b">
         <v>1</v>
       </c>
       <c r="B47" t="n">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>237_hgt-interim-report-and-accounts-2025.pdf</t>
+          <t>77_Annual%20report%202024.pdf</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -1227,52 +1227,52 @@
     </row>
     <row r="48">
       <c r="A48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" t="n">
-        <v>62</v>
-      </c>
-      <c r="C48" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>138_mondi-group-integrated-report-and-financial-statements-2023.pdf</t>
+        </is>
+      </c>
       <c r="D48" t="b">
         <v>0</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://ir.mi.com/system/files-encrypted/nasdaq_kms/assets/2025/04/24/5-27-15/%E8%8B%B1%E6%96%87.pdf'</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" t="n">
-        <v>101</v>
-      </c>
-      <c r="C49" t="inlineStr"/>
+        <v>236</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>236_IPCC_AR6_SYR_LongerReport.pdf</t>
+        </is>
+      </c>
       <c r="D49" t="b">
         <v>0</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.burberryplc.com/content/dam/burberryplc/corporate/2024-updates/burberry-annual-report-and-accounts-2023-24.pdf'</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="b">
         <v>1</v>
       </c>
       <c r="B50" t="n">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>78_GLEN-2024-Annual-Report.pdf</t>
+          <t>217_via-annual-report-2021-EN.pdf</t>
         </is>
       </c>
       <c r="D50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="inlineStr"/>
     </row>
@@ -1281,75 +1281,75 @@
         <v>1</v>
       </c>
       <c r="B51" t="n">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>254_steo_full.pdf</t>
+          <t>78_GLEN-2024-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" t="n">
-        <v>23</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>23_Annual-Report-2024.pdf</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="b">
         <v>0</v>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.cbs.dk:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="b">
         <v>1</v>
       </c>
       <c r="B53" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>58_annual-report-2024.pdf</t>
+          <t>61_loreal2024annualreport.pdf</t>
         </is>
       </c>
       <c r="D53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B54" t="n">
-        <v>257</v>
-      </c>
-      <c r="C54" t="inlineStr"/>
+        <v>256</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>256_i990.pdf</t>
+        </is>
+      </c>
       <c r="D54" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.mospi.gov.in:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="b">
         <v>0</v>
       </c>
       <c r="B55" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="b">
@@ -1357,41 +1357,41 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.fidelityinternational.com/legal/documents/FF/en/ar.ff.en.xx.pdf'</t>
+          <t>403, message='Forbidden', url='https://www.pwc.com/jm/en/research-publications/pdf/basic-understanding-of-a-companys-financials.pdf'</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B56" t="n">
-        <v>218</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>218_f940.pdf</t>
-        </is>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.nato.int/nato_static_fl2014/assets/pdf/2024/3/pdf/sgar23-en.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="b">
         <v>1</v>
       </c>
       <c r="B57" t="n">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>178_M-and-S-2023-Annual-Report.pdf</t>
+          <t>197_WEF_Future_of_Jobs_Report_2025.pdf</t>
         </is>
       </c>
       <c r="D57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr"/>
     </row>
@@ -1400,45 +1400,45 @@
         <v>1</v>
       </c>
       <c r="B58" t="n">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>155_gabriel_annual_report_2023-24.pdf</t>
+          <t>81_Beiersdorf-Annual-Report-2024.pdf</t>
         </is>
       </c>
       <c r="D58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B59" t="n">
-        <v>54</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>54_annual-report-2018.pdf</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://ir.mi.com/system/files-encrypted/nasdaq_kms/assets/2025/04/24/5-27-15/%E8%8B%B1%E6%96%87.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="b">
         <v>1</v>
       </c>
       <c r="B60" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>176_CIRO-Annual-Report-2024-2025-EN.pdf</t>
+          <t>178_M-and-S-2023-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -1448,31 +1448,31 @@
     </row>
     <row r="61">
       <c r="A61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="n">
-        <v>98</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>98_olam_annual_report_2024.pdf</t>
-        </is>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="b">
         <v>0</v>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.burberryplc.com/content/dam/burberryplc/corporate/2024-updates/burberry-annual-report-and-accounts-2023-24.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="b">
         <v>1</v>
       </c>
       <c r="B62" t="n">
-        <v>234</v>
+        <v>159</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>234_echapter.pdf</t>
+          <t>159_annual-report-2023-24.pdf</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -1482,20 +1482,20 @@
     </row>
     <row r="63">
       <c r="A63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B63" t="n">
-        <v>199</v>
-      </c>
-      <c r="C63" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>58_annual-report-2024.pdf</t>
+        </is>
+      </c>
       <c r="D63" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.epfo.gov.in/site_docs/Annual_Report/Annual_Report_2022-23.pdf'</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="b">
@@ -1516,52 +1516,52 @@
     </row>
     <row r="65">
       <c r="A65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B65" t="n">
-        <v>63</v>
-      </c>
-      <c r="C65" t="inlineStr"/>
+        <v>157</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>157_Inditex_Group_Annual_Accounts_2023.pdf</t>
+        </is>
+      </c>
       <c r="D65" t="b">
         <v>0</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Primary URL is not a valid PDF.</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B66" t="n">
-        <v>158</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>158_Annual-Report-2020_ENG1.pdf</t>
-        </is>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.mospi.gov.in:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="b">
         <v>1</v>
       </c>
       <c r="B67" t="n">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>141_Annual_Report_2021.pdf</t>
+          <t>98_olam_annual_report_2024.pdf</t>
         </is>
       </c>
       <c r="D67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="inlineStr"/>
     </row>
@@ -1570,11 +1570,11 @@
         <v>1</v>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>237</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>4_annual-report-nordea-bank-abp-2024-0.pdf</t>
+          <t>237_hgt-interim-report-and-accounts-2025.pdf</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -1587,11 +1587,11 @@
         <v>1</v>
       </c>
       <c r="B69" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>140_2637721.pdf</t>
+          <t>155_gabriel_annual_report_2023-24.pdf</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -1604,45 +1604,45 @@
         <v>1</v>
       </c>
       <c r="B70" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>81_Beiersdorf-Annual-Report-2024.pdf</t>
+          <t>135_currys-annual-report-2023-24-web.pdf</t>
         </is>
       </c>
       <c r="D70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B71" t="n">
-        <v>180</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>180_Annual-report-2023.pdf</t>
-        </is>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="b">
         <v>0</v>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.fidelityinternational.com/legal/documents/FF/en/ar.ff.en.xx.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="b">
         <v>1</v>
       </c>
       <c r="B72" t="n">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>258_Republic_Act_No_6713.pdf</t>
+          <t>218_f940.pdf</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -1652,31 +1652,31 @@
     </row>
     <row r="73">
       <c r="A73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B73" t="n">
-        <v>161</v>
-      </c>
-      <c r="C73" t="inlineStr"/>
+        <v>254</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>254_steo_full.pdf</t>
+        </is>
+      </c>
       <c r="D73" t="b">
         <v>0</v>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.bp.com/content/dam/bp/business-sites/en/global/corporate/pdfs/investors/bp-annual-report-and-form-20f-2019.pdf'</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="b">
         <v>1</v>
       </c>
       <c r="B74" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>42_250219-annual-report-and-accounts-2024.pdf</t>
+          <t>23_Annual-Report-2024.pdf</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -1689,11 +1689,11 @@
         <v>1</v>
       </c>
       <c r="B75" t="n">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>43_danske-bank---annual-report-2023.pdf</t>
+          <t>139_aig-2023-annual-report.pdf</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -1706,15 +1706,15 @@
         <v>0</v>
       </c>
       <c r="B76" t="n">
-        <v>5</v>
+        <v>199</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>404, message='Not Found', url='https://eifo.dk/media/f23eicl4/eifo-annual-report-2024.pdf'</t>
+          <t>403, message='Forbidden', url='https://www.epfo.gov.in/site_docs/Annual_Report/Annual_Report_2022-23.pdf'</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="n">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="b">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cannot connect to host www.sama.gov.sa:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+          <t>Primary URL is not a valid PDF.</t>
         </is>
       </c>
     </row>
@@ -1740,15 +1740,15 @@
         <v>1</v>
       </c>
       <c r="B78" t="n">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>200_250916---Annual-Report-2025.pdf</t>
+          <t>141_Annual_Report_2021.pdf</t>
         </is>
       </c>
       <c r="D78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="inlineStr"/>
     </row>
@@ -1757,45 +1757,45 @@
         <v>1</v>
       </c>
       <c r="B79" t="n">
-        <v>220</v>
+        <v>54</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>220_annual-report-2023.pdf</t>
+          <t>54_annual-report-2018.pdf</t>
         </is>
       </c>
       <c r="D79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
-      </c>
-      <c r="C80" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>160_2020-annual-report.pdf</t>
+        </is>
+      </c>
       <c r="D80" t="b">
         <v>1</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://investor.maersk.com/static-files/31bf05a1-6f0c-4fbd-a3c7-3f58e044f668'</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="b">
         <v>1</v>
       </c>
       <c r="B81" t="n">
-        <v>259</v>
+        <v>180</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>259_2025_ASR_PENN.pdf</t>
+          <t>180_Annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -1808,15 +1808,15 @@
         <v>1</v>
       </c>
       <c r="B82" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>64_annualreport-2024.pdf</t>
+          <t>42_250219-annual-report-and-accounts-2024.pdf</t>
         </is>
       </c>
       <c r="D82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr"/>
     </row>
@@ -1825,15 +1825,15 @@
         <v>1</v>
       </c>
       <c r="B83" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>239_IntegratedAnnualReport2024_Unofficial%20Version_Unaudited_0.pdf</t>
+          <t>258_Republic_Act_No_6713.pdf</t>
         </is>
       </c>
       <c r="D83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="inlineStr"/>
     </row>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="n">
-        <v>201</v>
+        <v>161</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="b">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.sec.gov/comments/s7-26-18/s72618-4826123-177031.pdf'</t>
+          <t>403, message='Forbidden', url='https://www.bp.com/content/dam/bp/business-sites/en/global/corporate/pdfs/investors/bp-annual-report-and-form-20f-2019.pdf'</t>
         </is>
       </c>
     </row>
@@ -1859,11 +1859,11 @@
         <v>1</v>
       </c>
       <c r="B85" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>123_ar-2024.pdf</t>
+          <t>140_2637721.pdf</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -1876,11 +1876,11 @@
         <v>1</v>
       </c>
       <c r="B86" t="n">
-        <v>240</v>
+        <v>43</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>240_2025-09-16-bernstein-ann.pdf</t>
+          <t>43_danske-bank---annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -1890,31 +1890,31 @@
     </row>
     <row r="87">
       <c r="A87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B87" t="n">
-        <v>83</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>83_nib-annual-report-2024.pdf</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="b">
-        <v>0</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://eifo.dk/media/f23eicl4/eifo-annual-report-2024.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="b">
         <v>1</v>
       </c>
       <c r="B88" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>162_2024-financial-statements-en.pdf</t>
+          <t>158_Annual-Report-2020_ENG1.pdf</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -1927,15 +1927,15 @@
         <v>1</v>
       </c>
       <c r="B89" t="n">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>160_2020-annual-report.pdf</t>
+          <t>4_annual-report-nordea-bank-abp-2024-0.pdf</t>
         </is>
       </c>
       <c r="D89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="inlineStr"/>
     </row>
@@ -1944,11 +1944,11 @@
         <v>1</v>
       </c>
       <c r="B90" t="n">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>143_2024-annual-report.pdf</t>
+          <t>59_annualreports-2021_en.pdf</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -1958,82 +1958,82 @@
     </row>
     <row r="91">
       <c r="A91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B91" t="n">
-        <v>221</v>
-      </c>
-      <c r="C91" t="inlineStr"/>
+        <v>102</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>102_Carnival-Corporation-plc-2024-Annual-Report.pdf</t>
+        </is>
+      </c>
       <c r="D91" t="b">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.bseindia.com/xml-data/corpfiling/AttachLive/7872a5ce-3f97-4e1b-a8f7-e5801677507c.pdf'</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B92" t="n">
-        <v>104</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>104_PhilipsFullAnnualReport2024-English.pdf</t>
-        </is>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="b">
         <v>0</v>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.sama.gov.sa:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="b">
         <v>1</v>
       </c>
       <c r="B93" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>121_Annual-Report-2022.pdf</t>
+          <t>122_Annual-Report-22.pdf</t>
         </is>
       </c>
       <c r="D93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B94" t="n">
-        <v>102</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>102_Carnival-Corporation-plc-2024-Annual-Report.pdf</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="b">
         <v>1</v>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://investor.maersk.com/static-files/31bf05a1-6f0c-4fbd-a3c7-3f58e044f668'</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="b">
         <v>1</v>
       </c>
       <c r="B95" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>260_SBCL_17092025111423_SBCL_Proceednigupdated.pdf</t>
+          <t>220_annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -2046,11 +2046,11 @@
         <v>1</v>
       </c>
       <c r="B96" t="n">
-        <v>182</v>
+        <v>259</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>182_kingfisher-annual-report-202324-pdf.pdf</t>
+          <t>259_2025_ASR_PENN.pdf</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -2060,65 +2060,65 @@
     </row>
     <row r="97">
       <c r="A97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B97" t="n">
-        <v>124</v>
-      </c>
-      <c r="C97" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>200_250916---Annual-Report-2025.pdf</t>
+        </is>
+      </c>
       <c r="D97" t="b">
         <v>0</v>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.reckitt.com/media/5qbh523b/annual-report-2022.pdf'</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="b">
         <v>1</v>
       </c>
       <c r="B98" t="n">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>179_Blender-Foundation-Annual-Report-2024.pdf</t>
+          <t>239_IntegratedAnnualReport2024_Unofficial%20Version_Unaudited_0.pdf</t>
         </is>
       </c>
       <c r="D98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B99" t="n">
-        <v>7</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>7_r1200appendix_d.pdf</t>
-        </is>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="b">
         <v>0</v>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.sec.gov/comments/s7-26-18/s72618-4826123-177031.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="b">
         <v>1</v>
       </c>
       <c r="B100" t="n">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>219_Digital_News-Report_2025.pdf</t>
+          <t>162_2024-financial-statements-en.pdf</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -2131,11 +2131,11 @@
         <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>45</v>
+        <v>240</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>45_annual_report_2020.pdf</t>
+          <t>240_2025-09-16-bernstein-ann.pdf</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -2148,11 +2148,11 @@
         <v>1</v>
       </c>
       <c r="B102" t="n">
-        <v>238</v>
+        <v>25</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>238_jpm-us-smaller-companies-web-hyr-2025.pdf</t>
+          <t>25_Small-Foundation-Annual-Report-2019.pdf</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -2165,11 +2165,11 @@
         <v>1</v>
       </c>
       <c r="B103" t="n">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>26_250219-annual-report-and-accounts-2024.pdf</t>
+          <t>84_dk-KPMG-Annual-report%202024_Digital-final.pdf</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -2182,11 +2182,11 @@
         <v>1</v>
       </c>
       <c r="B104" t="n">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>25_Small-Foundation-Annual-Report-2019.pdf</t>
+          <t>123_ar-2024.pdf</t>
         </is>
       </c>
       <c r="D104" t="b">
@@ -2199,11 +2199,11 @@
         <v>1</v>
       </c>
       <c r="B105" t="n">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>105_Annual_Report_AU_2021.pdf</t>
+          <t>143_2024-annual-report.pdf</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -2213,20 +2213,20 @@
     </row>
     <row r="106">
       <c r="A106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B106" t="n">
-        <v>144</v>
-      </c>
-      <c r="C106" t="inlineStr"/>
+        <v>104</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>104_PhilipsFullAnnualReport2024-English.pdf</t>
+        </is>
+      </c>
       <c r="D106" t="b">
         <v>0</v>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.experianplc.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="b">
@@ -2250,11 +2250,11 @@
         <v>1</v>
       </c>
       <c r="B108" t="n">
-        <v>122</v>
+        <v>260</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>122_Annual-Report-22.pdf</t>
+          <t>260_SBCL_17092025111423_SBCL_Proceednigupdated.pdf</t>
         </is>
       </c>
       <c r="D108" t="b">
@@ -2267,11 +2267,11 @@
         <v>1</v>
       </c>
       <c r="B109" t="n">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>163_dwp_annual_report_and_accounts_2023_2024.pdf</t>
+          <t>21_Inditex_Group_Annual_Report_2024.pdf</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -2281,31 +2281,31 @@
     </row>
     <row r="110">
       <c r="A110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B110" t="n">
-        <v>66</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>66_sw-2024-annual-report.pdf</t>
-        </is>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="b">
-        <v>1</v>
-      </c>
-      <c r="E110" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.bseindia.com/xml-data/corpfiling/AttachLive/7872a5ce-3f97-4e1b-a8f7-e5801677507c.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="b">
         <v>1</v>
       </c>
       <c r="B111" t="n">
-        <v>261</v>
+        <v>45</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>261_gc69_schedule_monday.pdf</t>
+          <t>45_annual_report_2020.pdf</t>
         </is>
       </c>
       <c r="D111" t="b">
@@ -2315,52 +2315,52 @@
     </row>
     <row r="112">
       <c r="A112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B112" t="n">
-        <v>177</v>
-      </c>
-      <c r="C112" t="inlineStr"/>
+        <v>121</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>121_Annual-Report-2022.pdf</t>
+        </is>
+      </c>
       <c r="D112" t="b">
-        <v>0</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Cannot connect to host lewisgroup.co.za:443 ssl:default [The semaphore timeout period has expired]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B113" t="n">
-        <v>8</v>
-      </c>
-      <c r="C113" t="inlineStr"/>
+        <v>219</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>219_Digital_News-Report_2025.pdf</t>
+        </is>
+      </c>
       <c r="D113" t="b">
-        <v>1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.unilever.com/files/unilever-annual-report-and-accounts-2024.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="b">
         <v>1</v>
       </c>
       <c r="B114" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>46_guide-to-understanding-annual-reporting.pdf</t>
+          <t>7_r1200appendix_d.pdf</t>
         </is>
       </c>
       <c r="D114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="n">
-        <v>242</v>
+        <v>124</v>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="b">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.accc.gov.au/system/files/accc-aer-audit-risk-committee-charter-august-2025.pdf'</t>
+          <t>404, message='Not Found', url='https://www.reckitt.com/media/5qbh523b/annual-report-2022.pdf'</t>
         </is>
       </c>
     </row>
@@ -2386,11 +2386,11 @@
         <v>1</v>
       </c>
       <c r="B116" t="n">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>202_Woolworths%20Group%20Annual%20Report%202025%20.pdf</t>
+          <t>181_annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D116" t="b">
@@ -2400,48 +2400,48 @@
     </row>
     <row r="117">
       <c r="A117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B117" t="n">
-        <v>125</v>
-      </c>
-      <c r="C117" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>24_heineken_n_v_annual_report_2024_final_20feb2025.pdf</t>
+        </is>
+      </c>
       <c r="D117" t="b">
-        <v>1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.unilever.com/files/33321193-0d9a-44dd-93f8-02209fc6bd54/annual-report-and-accounts-2021.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B118" t="n">
-        <v>27</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>27_2024-informa-annual-report.pdf</t>
-        </is>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="b">
         <v>0</v>
       </c>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.experianplc.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="b">
         <v>1</v>
       </c>
       <c r="B119" t="n">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>181_annual-report-2023.pdf</t>
+          <t>26_250219-annual-report-and-accounts-2024.pdf</t>
         </is>
       </c>
       <c r="D119" t="b">
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="b">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.rlb.dk/'</t>
+          <t>Cannot connect to host lewisgroup.co.za:443 ssl:default [The semaphore timeout period has expired]</t>
         </is>
       </c>
     </row>
@@ -2471,11 +2471,11 @@
         <v>1</v>
       </c>
       <c r="B121" t="n">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>145_SG-Annual-Report-on-the-work-of-the-Organization.pdf</t>
+          <t>83_nib-annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D121" t="b">
@@ -2488,11 +2488,11 @@
         <v>1</v>
       </c>
       <c r="B122" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>85_ihg-ar-2024.pdf</t>
+          <t>105_Annual_Report_AU_2021.pdf</t>
         </is>
       </c>
       <c r="D122" t="b">
@@ -2505,15 +2505,15 @@
         <v>1</v>
       </c>
       <c r="B123" t="n">
-        <v>203</v>
+        <v>66</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>203_38c6e738-8eda-11f0-a482-6e440358bbe4.pdf</t>
+          <t>66_sw-2024-annual-report.pdf</t>
         </is>
       </c>
       <c r="D123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" t="inlineStr"/>
     </row>
@@ -2522,15 +2522,15 @@
         <v>1</v>
       </c>
       <c r="B124" t="n">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>222_MPA-2021-THEME-Report-FINAL.pdf</t>
+          <t>179_Blender-Foundation-Annual-Report-2024.pdf</t>
         </is>
       </c>
       <c r="D124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" t="inlineStr"/>
     </row>
@@ -2539,11 +2539,11 @@
         <v>1</v>
       </c>
       <c r="B125" t="n">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>65_aa-annual-report-full-2024.pdf</t>
+          <t>261_gc69_schedule_monday.pdf</t>
         </is>
       </c>
       <c r="D125" t="b">
@@ -2556,15 +2556,15 @@
         <v>1</v>
       </c>
       <c r="B126" t="n">
-        <v>262</v>
+        <v>46</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>262_07d4ee9c-934c-11f0-8802-ae41b78b60fd.pdf</t>
+          <t>46_guide-to-understanding-annual-reporting.pdf</t>
         </is>
       </c>
       <c r="D126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr"/>
     </row>
@@ -2573,62 +2573,58 @@
         <v>0</v>
       </c>
       <c r="B127" t="n">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="b">
-        <v>1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://group.mercedes-benz.com/documents/investors/reports/annual-report/mercedes-benz/mercedes-benz-annual-report-2023-incl-combined-management-report-mbg-ag.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="b">
         <v>0</v>
       </c>
       <c r="B128" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Primary URL is not a valid PDF.</t>
+          <t>403, message='Forbidden', url='https://www.unilever.com/files/unilever-annual-report-and-accounts-2024.pdf'</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B129" t="n">
-        <v>84</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>84_dk-KPMG-Annual-report%202024_Digital-final.pdf</t>
-        </is>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="b">
-        <v>0</v>
-      </c>
-      <c r="E129" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.unilever.com/files/33321193-0d9a-44dd-93f8-02209fc6bd54/annual-report-and-accounts-2021.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="b">
         <v>1</v>
       </c>
       <c r="B130" t="n">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>243_0001140361-25-035121.pdf</t>
+          <t>163_dwp_annual_report_and_accounts_2023_2024.pdf</t>
         </is>
       </c>
       <c r="D130" t="b">
@@ -2641,11 +2637,11 @@
         <v>1</v>
       </c>
       <c r="B131" t="n">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>183_259396.pdf</t>
+          <t>85_ihg-ar-2024.pdf</t>
         </is>
       </c>
       <c r="D131" t="b">
@@ -2655,65 +2651,65 @@
     </row>
     <row r="132">
       <c r="A132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B132" t="n">
-        <v>68</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>68_202505020944401774654665_en.pdf</t>
-        </is>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="b">
         <v>0</v>
       </c>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.accc.gov.au/system/files/accc-aer-audit-risk-committee-charter-august-2025.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B133" t="n">
-        <v>165</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>165_richemont-fy24-annual-report-en.pdf</t>
-        </is>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="b">
         <v>0</v>
       </c>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Primary URL is not a valid PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B134" t="n">
-        <v>185</v>
-      </c>
-      <c r="C134" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>65_aa-annual-report-full-2024.pdf</t>
+        </is>
+      </c>
       <c r="D134" t="b">
-        <v>1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Cannot connect to host labour.gov.in:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="b">
         <v>1</v>
       </c>
       <c r="B135" t="n">
-        <v>224</v>
+        <v>27</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>224_annual-report-2023-24.pdf</t>
+          <t>27_2024-informa-annual-report.pdf</t>
         </is>
       </c>
       <c r="D135" t="b">
@@ -2723,35 +2719,35 @@
     </row>
     <row r="136">
       <c r="A136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B136" t="n">
-        <v>10</v>
-      </c>
-      <c r="C136" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>182_kingfisher-annual-report-202324-pdf.pdf</t>
+        </is>
+      </c>
       <c r="D136" t="b">
-        <v>1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>429, message='Too Many Requests', url='https://zerodha.com/varsity/chapter/read-annual-report-company/'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="b">
         <v>1</v>
       </c>
       <c r="B137" t="n">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>164_atea-annual-report-2021.pdf</t>
+          <t>145_SG-Annual-Report-on-the-work-of-the-Organization.pdf</t>
         </is>
       </c>
       <c r="D137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="inlineStr"/>
     </row>
@@ -2760,15 +2756,15 @@
         <v>1</v>
       </c>
       <c r="B138" t="n">
-        <v>106</v>
+        <v>183</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>106_10610-001-BPTA_Best-practice-2014-15_FINAL.pdf</t>
+          <t>183_259396.pdf</t>
         </is>
       </c>
       <c r="D138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="inlineStr"/>
     </row>
@@ -2777,11 +2773,11 @@
         <v>1</v>
       </c>
       <c r="B139" t="n">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>166_2020ar.pdf</t>
+          <t>202_Woolworths%20Group%20Annual%20Report%202025%20.pdf</t>
         </is>
       </c>
       <c r="D139" t="b">
@@ -2794,45 +2790,45 @@
         <v>1</v>
       </c>
       <c r="B140" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>21_Inditex_Group_Annual_Report_2024.pdf</t>
+          <t>64_annualreport-2024.pdf</t>
         </is>
       </c>
       <c r="D140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B141" t="n">
-        <v>107</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>107_2025-04-08_BDO-Arsrapport2023_24_ENGELSK.pdf</t>
-        </is>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="b">
-        <v>0</v>
-      </c>
-      <c r="E141" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://group.mercedes-benz.com/documents/investors/reports/annual-report/mercedes-benz/mercedes-benz-annual-report-2023-incl-combined-management-report-mbg-ag.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="b">
         <v>1</v>
       </c>
       <c r="B142" t="n">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>87_atea-annual-report-2024.pdf</t>
+          <t>203_38c6e738-8eda-11f0-a482-6e440358bbe4.pdf</t>
         </is>
       </c>
       <c r="D142" t="b">
@@ -2842,31 +2838,31 @@
     </row>
     <row r="143">
       <c r="A143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B143" t="n">
-        <v>146</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>146_BOI-Annual-Report-2020.pdf</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="b">
         <v>0</v>
       </c>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Primary URL is not a valid PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="b">
         <v>1</v>
       </c>
       <c r="B144" t="n">
-        <v>127</v>
+        <v>243</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>127_daa-Annual-Report-2024-ENG-Web.pdf</t>
+          <t>243_0001140361-25-035121.pdf</t>
         </is>
       </c>
       <c r="D144" t="b">
@@ -2876,35 +2872,35 @@
     </row>
     <row r="145">
       <c r="A145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B145" t="n">
-        <v>30</v>
-      </c>
-      <c r="C145" t="inlineStr"/>
+        <v>107</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>107_2025-04-08_BDO-Arsrapport2023_24_ENGELSK.pdf</t>
+        </is>
+      </c>
       <c r="D145" t="b">
         <v>0</v>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.boeing.com/content/dam/boeing/boeingdotcom/company/annual-report/2024/2024-annual-report.pdf'</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="b">
         <v>1</v>
       </c>
       <c r="B146" t="n">
-        <v>244</v>
+        <v>106</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>244_Annual-CSR-Report-2023-24.pdf</t>
+          <t>106_10610-001-BPTA_Best-practice-2014-15_FINAL.pdf</t>
         </is>
       </c>
       <c r="D146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" t="inlineStr"/>
     </row>
@@ -2913,11 +2909,11 @@
         <v>1</v>
       </c>
       <c r="B147" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>147_inter-ikea-holding-bv-annual-report-fy24.pdf</t>
+          <t>165_richemont-fy24-annual-report-en.pdf</t>
         </is>
       </c>
       <c r="D147" t="b">
@@ -2930,11 +2926,11 @@
         <v>1</v>
       </c>
       <c r="B148" t="n">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>126_agm-dsmfirmenich-integrated-annual-report-2023.pdf</t>
+          <t>68_202505020944401774654665_en.pdf</t>
         </is>
       </c>
       <c r="D148" t="b">
@@ -2947,11 +2943,11 @@
         <v>1</v>
       </c>
       <c r="B149" t="n">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>186_2023-informa-annual-report.pdf</t>
+          <t>222_MPA-2021-THEME-Report-FINAL.pdf</t>
         </is>
       </c>
       <c r="D149" t="b">
@@ -2964,15 +2960,15 @@
         <v>1</v>
       </c>
       <c r="B150" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>69_2024-annual-report.pdf</t>
+          <t>164_atea-annual-report-2021.pdf</t>
         </is>
       </c>
       <c r="D150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" t="inlineStr"/>
     </row>
@@ -2981,15 +2977,15 @@
         <v>0</v>
       </c>
       <c r="B151" t="n">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Cannot connect to host en-rules.hkex.com.hk:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+          <t>Secondary URL is not a valid PDF.</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="B152" t="n">
-        <v>263</v>
+        <v>185</v>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="b">
@@ -3006,7 +3002,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.idx.co.id/Portals/0/StaticData/ListedCompanies/Corporate_Actions/New_Info_JSX/Jenis_Informasi/01_Laporan_Keuangan/04_Annual%20Report/2018/INDF/INDF_Annual%20Report_2018.pdf'</t>
+          <t>Cannot connect to host labour.gov.in:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
         </is>
       </c>
     </row>
@@ -3015,11 +3011,11 @@
         <v>1</v>
       </c>
       <c r="B153" t="n">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>48_Ryanair-2023-Annual-Report.pdf</t>
+          <t>224_annual-report-2023-24.pdf</t>
         </is>
       </c>
       <c r="D153" t="b">
@@ -3029,31 +3025,31 @@
     </row>
     <row r="154">
       <c r="A154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B154" t="n">
-        <v>128</v>
-      </c>
-      <c r="C154" t="inlineStr"/>
+        <v>262</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>262_07d4ee9c-934c-11f0-8802-ae41b78b60fd.pdf</t>
+        </is>
+      </c>
       <c r="D154" t="b">
-        <v>1</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.merckgroup.com/investors/reports-and-financials/earnings-materials/2022-q4/en/2022-Q4-Report-EN.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="b">
         <v>1</v>
       </c>
       <c r="B155" t="n">
-        <v>264</v>
+        <v>146</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>264_Global-Peace-Index-2025-web.pdf</t>
+          <t>146_BOI-Annual-Report-2020.pdf</t>
         </is>
       </c>
       <c r="D155" t="b">
@@ -3066,11 +3062,11 @@
         <v>1</v>
       </c>
       <c r="B156" t="n">
-        <v>205</v>
+        <v>87</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>205_annual-report-2023-extract---pensiondanmark.pdf</t>
+          <t>87_atea-annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D156" t="b">
@@ -3083,11 +3079,11 @@
         <v>1</v>
       </c>
       <c r="B157" t="n">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>108_amNsb3VkczovLzAzLzMxLzhmLzkyLzFhLzc5NTMtNDQzZS1hMmFlLTgxNWRlYWVkNGNlOQ.pdf</t>
+          <t>166_2020ar.pdf</t>
         </is>
       </c>
       <c r="D157" t="b">
@@ -3100,45 +3096,45 @@
         <v>1</v>
       </c>
       <c r="B158" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>9_carlsberg-breweries-group_2024-annual-report.pdf</t>
+          <t>48_Ryanair-2023-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B159" t="n">
-        <v>89</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>89_form_06_com_-_annual_report.pdf</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="b">
-        <v>1</v>
-      </c>
-      <c r="E159" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.boeing.com/content/dam/boeing/boeingdotcom/company/annual-report/2024/2024-annual-report.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="b">
         <v>1</v>
       </c>
       <c r="B160" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>109_annual-report-2020-21.pdf</t>
+          <t>88_statkraft-as---annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D160" t="b">
@@ -3151,11 +3147,11 @@
         <v>1</v>
       </c>
       <c r="B161" t="n">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>47_annual-report-2022.pdf</t>
+          <t>127_daa-Annual-Report-2024-ENG-Web.pdf</t>
         </is>
       </c>
       <c r="D161" t="b">
@@ -3165,50 +3161,54 @@
     </row>
     <row r="162">
       <c r="A162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B162" t="n">
-        <v>265</v>
-      </c>
-      <c r="C162" t="inlineStr"/>
+        <v>147</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>147_inter-ikea-holding-bv-annual-report-fy24.pdf</t>
+        </is>
+      </c>
       <c r="D162" t="b">
         <v>0</v>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.ssa.gov/forms/ssa-7050.pdf'</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B163" t="n">
-        <v>22</v>
-      </c>
-      <c r="C163" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>186_2023-informa-annual-report.pdf</t>
+        </is>
+      </c>
       <c r="D163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B164" t="n">
-        <v>31</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>31_tdc-net-annual-report-2023.pdf</t>
-        </is>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="b">
         <v>0</v>
       </c>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Cannot connect to host en-rules.hkex.com.hk:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="b">
@@ -3232,83 +3232,83 @@
         <v>1</v>
       </c>
       <c r="B166" t="n">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>167_LH-AR-2021-e.pdf</t>
+          <t>69_2024-annual-report.pdf</t>
         </is>
       </c>
       <c r="D166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B167" t="n">
-        <v>129</v>
-      </c>
-      <c r="C167" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>205_annual-report-2023-extract---pensiondanmark.pdf</t>
+        </is>
+      </c>
       <c r="D167" t="b">
         <v>0</v>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://corporate.mcdonalds.com/content/dam/sites/corp/nfl/pdf/McD%20-%202024%20Annual%20Report%20to%20Shareholders.pdf'</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B168" t="n">
-        <v>88</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>88_statkraft-as---annual-report-2024.pdf</t>
-        </is>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="b">
-        <v>0</v>
-      </c>
-      <c r="E168" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.merckgroup.com/investors/reports-and-financials/earnings-materials/2022-q4/en/2022-Q4-Report-EN.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B169" t="n">
-        <v>90</v>
-      </c>
-      <c r="C169" t="inlineStr"/>
+        <v>108</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>108_amNsb3VkczovLzAzLzMxLzhmLzkyLzFhLzc5NTMtNDQzZS1hMmFlLTgxNWRlYWVkNGNlOQ.pdf</t>
+        </is>
+      </c>
       <c r="D169" t="b">
         <v>0</v>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Cannot connect to host annualreport2024.volkswagen-group.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="b">
         <v>1</v>
       </c>
       <c r="B170" t="n">
-        <v>168</v>
+        <v>89</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>168_Aarsrapport_2023_engelsk_2024.pdf</t>
+          <t>89_form_06_com_-_annual_report.pdf</t>
         </is>
       </c>
       <c r="D170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E170" t="inlineStr"/>
     </row>
@@ -3317,45 +3317,45 @@
         <v>0</v>
       </c>
       <c r="B171" t="n">
-        <v>207</v>
+        <v>263</v>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>404, message='Not Found', url='https://cdn.rigsrevisionen.dk/rigsrevisionen/Media/638229369267919065/Annual-report-2022.pdf'</t>
+          <t>403, message='Forbidden', url='https://www.idx.co.id/Portals/0/StaticData/ListedCompanies/Corporate_Actions/New_Info_JSX/Jenis_Informasi/01_Laporan_Keuangan/04_Annual%20Report/2018/INDF/INDF_Annual%20Report_2018.pdf'</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B172" t="n">
-        <v>71</v>
-      </c>
-      <c r="C172" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>264_Global-Peace-Index-2025-web.pdf</t>
+        </is>
+      </c>
       <c r="D172" t="b">
-        <v>1</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.hul.co.in/files/hul-integrated-annual-report-2024-25.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="b">
         <v>1</v>
       </c>
       <c r="B173" t="n">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>187_annualreport-2023.pdf</t>
+          <t>109_annual-report-2020-21.pdf</t>
         </is>
       </c>
       <c r="D173" t="b">
@@ -3368,15 +3368,15 @@
         <v>1</v>
       </c>
       <c r="B174" t="n">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>110_nykredit_q4_24_2025-02-05_en.pdf</t>
+          <t>167_LH-AR-2021-e.pdf</t>
         </is>
       </c>
       <c r="D174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" t="inlineStr"/>
     </row>
@@ -3385,11 +3385,11 @@
         <v>1</v>
       </c>
       <c r="B175" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>70_MunichRe-Group-Annual-Report-2024-en.pdf</t>
+          <t>47_annual-report-2022.pdf</t>
         </is>
       </c>
       <c r="D175" t="b">
@@ -3399,18 +3399,14 @@
     </row>
     <row r="176">
       <c r="A176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B176" t="n">
-        <v>246</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>246_SDG_India_Index_2023-24.pdf</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C176" t="inlineStr"/>
       <c r="D176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E176" t="inlineStr"/>
     </row>
@@ -3419,11 +3415,11 @@
         <v>1</v>
       </c>
       <c r="B177" t="n">
-        <v>226</v>
+        <v>103</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>226_240226-annual-report-and-accounts-2023.pdf</t>
+          <t>103_Informe-anual-2024_ENG.pdf</t>
         </is>
       </c>
       <c r="D177" t="b">
@@ -3433,48 +3429,48 @@
     </row>
     <row r="178">
       <c r="A178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B178" t="n">
-        <v>13</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>13_2024ar.pdf</t>
-        </is>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="C178" t="inlineStr"/>
       <c r="D178" t="b">
         <v>0</v>
       </c>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.ssa.gov/forms/ssa-7050.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B179" t="n">
-        <v>266</v>
-      </c>
-      <c r="C179" t="inlineStr"/>
+        <v>244</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>244_Annual-CSR-Report-2023-24.pdf</t>
+        </is>
+      </c>
       <c r="D179" t="b">
-        <v>1</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.adobe.com/cc-shared/assets/investor-relations/pdfs/11905202/aiy4w5teshy5t.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="b">
         <v>1</v>
       </c>
       <c r="B180" t="n">
-        <v>206</v>
+        <v>126</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>206_full-report.pdf</t>
+          <t>126_agm-dsmfirmenich-integrated-annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D180" t="b">
@@ -3484,150 +3480,150 @@
     </row>
     <row r="181">
       <c r="A181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B181" t="n">
-        <v>91</v>
-      </c>
-      <c r="C181" t="inlineStr"/>
+        <v>187</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>187_annualreport-2023.pdf</t>
+        </is>
+      </c>
       <c r="D181" t="b">
         <v>0</v>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Primary URL is not a valid PDF.</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B182" t="n">
-        <v>227</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>227_2023-Annual-Report.pdf</t>
-        </is>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="b">
-        <v>1</v>
-      </c>
-      <c r="E182" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://corporate.mcdonalds.com/content/dam/sites/corp/nfl/pdf/McD%20-%202024%20Annual%20Report%20to%20Shareholders.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B183" t="n">
-        <v>208</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>208_ghg-protocol-revised.pdf</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="b">
         <v>0</v>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Cannot connect to host annualreport2024.volkswagen-group.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B184" t="n">
-        <v>247</v>
-      </c>
-      <c r="C184" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>70_MunichRe-Group-Annual-Report-2024-en.pdf</t>
+        </is>
+      </c>
       <c r="D184" t="b">
         <v>0</v>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Cannot connect to host ncert.nic.in:443 ssl:default [The specified network name is no longer available]</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B185" t="n">
-        <v>111</v>
-      </c>
-      <c r="C185" t="inlineStr"/>
+        <v>238</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>238_jpm-us-smaller-companies-web-hyr-2025.pdf</t>
+        </is>
+      </c>
       <c r="D185" t="b">
         <v>0</v>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.adobe.com/cc-shared/assets/investor-relations/pdfs/adbe-2024-annual-report.pdf'</t>
-        </is>
-      </c>
+      <c r="E185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="b">
         <v>1</v>
       </c>
       <c r="B186" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>32_gabriel_annual_report_2022-23.pdf</t>
+          <t>86_BAT_Annual_Report_on_Form_20-F_2024.pdf</t>
         </is>
       </c>
       <c r="D186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B187" t="n">
-        <v>72</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>72_fs_uk_year2020.pdf</t>
-        </is>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="b">
         <v>0</v>
       </c>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://cdn.rigsrevisionen.dk/rigsrevisionen/Media/638229369267919065/Annual-report-2022.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B188" t="n">
-        <v>188</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>188_bn_annual_report_2023.pdf</t>
-        </is>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="b">
-        <v>0</v>
-      </c>
-      <c r="E188" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.hul.co.in/files/hul-integrated-annual-report-2024-25.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="b">
         <v>1</v>
       </c>
       <c r="B189" t="n">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>130_240412.pdf</t>
+          <t>168_Aarsrapport_2023_engelsk_2024.pdf</t>
         </is>
       </c>
       <c r="D189" t="b">
@@ -3637,31 +3633,31 @@
     </row>
     <row r="190">
       <c r="A190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B190" t="n">
-        <v>228</v>
-      </c>
-      <c r="C190" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>226_240226-annual-report-and-accounts-2023.pdf</t>
+        </is>
+      </c>
       <c r="D190" t="b">
         <v>0</v>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.michigan.gov/treasury/-/media/Project/Websites/treasury/BLGSS/LAFD/Webinar/FY25/Fundamentals-to-Best-Practices-Slides.pdf'</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="b">
         <v>1</v>
       </c>
       <c r="B191" t="n">
-        <v>267</v>
+        <v>31</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>267_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
+          <t>31_tdc-net-annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D191" t="b">
@@ -3674,11 +3670,11 @@
         <v>1</v>
       </c>
       <c r="B192" t="n">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>150_annual-reports-one-pager.pdf</t>
+          <t>13_2024ar.pdf</t>
         </is>
       </c>
       <c r="D192" t="b">
@@ -3688,29 +3684,33 @@
     </row>
     <row r="193">
       <c r="A193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B193" t="n">
-        <v>12</v>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>12_annual-report-2024.pdf</t>
-        </is>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="b">
-        <v>0</v>
-      </c>
-      <c r="E193" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.adobe.com/cc-shared/assets/investor-relations/pdfs/11905202/aiy4w5teshy5t.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B194" t="n">
-        <v>24</v>
-      </c>
-      <c r="C194" t="inlineStr"/>
+        <v>206</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>206_full-report.pdf</t>
+        </is>
+      </c>
       <c r="D194" t="b">
         <v>0</v>
       </c>
@@ -3718,65 +3718,65 @@
     </row>
     <row r="195">
       <c r="A195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B195" t="n">
-        <v>11</v>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>11_annual-report-adidas-ar24.pdf</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="b">
         <v>0</v>
       </c>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Primary URL is not a valid PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="b">
         <v>1</v>
       </c>
       <c r="B196" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>50_Annual-Report-2023.pdf</t>
+          <t>9_carlsberg-breweries-group_2024-annual-report.pdf</t>
         </is>
       </c>
       <c r="D196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B197" t="n">
-        <v>170</v>
-      </c>
-      <c r="C197" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>11_annual-report-adidas-ar24.pdf</t>
+        </is>
+      </c>
       <c r="D197" t="b">
         <v>0</v>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.pwc.se/sv/om-oss/annual-report-2023-2024.pdf'</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="b">
         <v>1</v>
       </c>
       <c r="B198" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>34_10-Q4-2024-As-Filed.pdf</t>
+          <t>12_annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D198" t="b">
@@ -3786,31 +3786,31 @@
     </row>
     <row r="199">
       <c r="A199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B199" t="n">
-        <v>148</v>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>148_diageo-annual-report-2024.pdf</t>
-        </is>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="b">
         <v>0</v>
       </c>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Cannot connect to host ncert.nic.in:443 ssl:default [The specified network name is no longer available]</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="b">
         <v>1</v>
       </c>
       <c r="B200" t="n">
-        <v>245</v>
+        <v>148</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>245_The-Sustainable-Development-Goals-Report-2025.pdf</t>
+          <t>148_diageo-annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D200" t="b">
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="B201" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="b">
@@ -3831,18 +3831,22 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.parliament.uk/globalassets/documents/commons-expenditure/admin-annual-accounts/administration_annual_report_and_accounts_2022_23-accessible.pdf'</t>
+          <t>403, message='Forbidden', url='https://www.adobe.com/cc-shared/assets/investor-relations/pdfs/adbe-2024-annual-report.pdf'</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B202" t="n">
-        <v>103</v>
-      </c>
-      <c r="C202" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>110_nykredit_q4_24_2025-02-05_en.pdf</t>
+        </is>
+      </c>
       <c r="D202" t="b">
         <v>0</v>
       </c>
@@ -3853,11 +3857,11 @@
         <v>1</v>
       </c>
       <c r="B203" t="n">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>248_Macfarlane-Group-PLC-Interim-Report-2025.pdf</t>
+          <t>169_FS_Group_2023_Annual_Report.pdf</t>
         </is>
       </c>
       <c r="D203" t="b">
@@ -3870,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="b">
@@ -3878,7 +3882,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>404, message='Not Found', url='https://www.eif.org/files/records/eif-annual-report-2021.pdf'</t>
+          <t>403, message='Forbidden', url='https://www.michigan.gov/treasury/-/media/Project/Websites/treasury/BLGSS/LAFD/Webinar/FY25/Fundamentals-to-Best-Practices-Slides.pdf'</t>
         </is>
       </c>
     </row>
@@ -3887,15 +3891,15 @@
         <v>1</v>
       </c>
       <c r="B205" t="n">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>169_FS_Group_2023_Annual_Report.pdf</t>
+          <t>227_2023-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E205" t="inlineStr"/>
     </row>
@@ -3904,15 +3908,15 @@
         <v>1</v>
       </c>
       <c r="B206" t="n">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>189_0001193125-24-092555.pdf</t>
+          <t>267_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
         </is>
       </c>
       <c r="D206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E206" t="inlineStr"/>
     </row>
@@ -3921,11 +3925,11 @@
         <v>1</v>
       </c>
       <c r="B207" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>190_RMTF_2024-25_FINAL.pdf</t>
+          <t>150_annual-reports-one-pager.pdf</t>
         </is>
       </c>
       <c r="D207" t="b">
@@ -3938,15 +3942,15 @@
         <v>1</v>
       </c>
       <c r="B208" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>14_richemont-fy25-annual-report-en.pdf</t>
+          <t>72_fs_uk_year2020.pdf</t>
         </is>
       </c>
       <c r="D208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E208" t="inlineStr"/>
     </row>
@@ -3955,11 +3959,11 @@
         <v>1</v>
       </c>
       <c r="B209" t="n">
-        <v>268</v>
+        <v>130</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>268_budget_speech.pdf</t>
+          <t>130_240412.pdf</t>
         </is>
       </c>
       <c r="D209" t="b">
@@ -3972,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="B210" t="n">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="b">
@@ -3980,37 +3984,37 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.economie.gouv.fr/files/files/directions_services/agence-participations-etat/Documents/Rapports-de-l-Etat-actionnaire/2023/REA2023_Ang-web.pdf?v=1705416463'</t>
+          <t>403, message='Forbidden', url='https://www.pwc.se/sv/om-oss/annual-report-2023-2024.pdf'</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B211" t="n">
-        <v>171</v>
-      </c>
-      <c r="C211" t="inlineStr"/>
+        <v>208</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>208_ghg-protocol-revised.pdf</t>
+        </is>
+      </c>
       <c r="D211" t="b">
         <v>0</v>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>Primary URL is not a valid PDF.</t>
-        </is>
-      </c>
+      <c r="E211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="b">
         <v>1</v>
       </c>
       <c r="B212" t="n">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>86_BAT_Annual_Report_on_Form_20-F_2024.pdf</t>
+          <t>14_richemont-fy25-annual-report-en.pdf</t>
         </is>
       </c>
       <c r="D212" t="b">
@@ -4023,11 +4027,11 @@
         <v>1</v>
       </c>
       <c r="B213" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>33_annual-report-2023.pdf</t>
+          <t>34_10-Q4-2024-As-Filed.pdf</t>
         </is>
       </c>
       <c r="D213" t="b">
@@ -4040,11 +4044,11 @@
         <v>1</v>
       </c>
       <c r="B214" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>249_InvestorDay2025.pdf</t>
+          <t>248_Macfarlane-Group-PLC-Interim-Report-2025.pdf</t>
         </is>
       </c>
       <c r="D214" t="b">
@@ -4057,11 +4061,11 @@
         <v>1</v>
       </c>
       <c r="B215" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>73_annual-report-2024-e.pdf</t>
+          <t>33_annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D215" t="b">
@@ -4071,20 +4075,20 @@
     </row>
     <row r="216">
       <c r="A216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B216" t="n">
-        <v>113</v>
-      </c>
-      <c r="C216" t="inlineStr"/>
+        <v>245</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>245_The-Sustainable-Development-Goals-Report-2025.pdf</t>
+        </is>
+      </c>
       <c r="D216" t="b">
-        <v>1</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.bhp.com/-/media/documents/investors/annual-reports/2019/bhpannualreport2019.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="b">
@@ -4105,31 +4109,31 @@
     </row>
     <row r="218">
       <c r="A218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B218" t="n">
-        <v>209</v>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>209_94fcfb43-c9be-4d9a-8d43-2fa983be69fa.pdf</t>
-        </is>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C218" t="inlineStr"/>
       <c r="D218" t="b">
-        <v>1</v>
-      </c>
-      <c r="E218" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.eif.org/files/records/eif-annual-report-2021.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="b">
         <v>1</v>
       </c>
       <c r="B219" t="n">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>53_puma-annual-report-2024-en-final.pdf</t>
+          <t>188_bn_annual_report_2023.pdf</t>
         </is>
       </c>
       <c r="D219" t="b">
@@ -4139,35 +4143,35 @@
     </row>
     <row r="220">
       <c r="A220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B220" t="n">
-        <v>55</v>
-      </c>
-      <c r="C220" t="inlineStr"/>
+        <v>268</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>268_budget_speech.pdf</t>
+        </is>
+      </c>
       <c r="D220" t="b">
         <v>0</v>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.ey.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+      <c r="E220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="b">
         <v>1</v>
       </c>
       <c r="B221" t="n">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>35_Barclays-PLC-Annual-Report-2024.pdf</t>
+          <t>190_RMTF_2024-25_FINAL.pdf</t>
         </is>
       </c>
       <c r="D221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221" t="inlineStr"/>
     </row>
@@ -4176,11 +4180,11 @@
         <v>1</v>
       </c>
       <c r="B222" t="n">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>74_LH-AR-2024-e.pdf</t>
+          <t>112_administration_annual_report_and_accounts_2022_23-accessible.pdf</t>
         </is>
       </c>
       <c r="D222" t="b">
@@ -4193,15 +4197,15 @@
         <v>1</v>
       </c>
       <c r="B223" t="n">
-        <v>152</v>
+        <v>209</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>152_Ryanair-2019-Annual-Report.pdf</t>
+          <t>209_94fcfb43-c9be-4d9a-8d43-2fa983be69fa.pdf</t>
         </is>
       </c>
       <c r="D223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E223" t="inlineStr"/>
     </row>
@@ -4210,11 +4214,11 @@
         <v>1</v>
       </c>
       <c r="B224" t="n">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>94_bsc-2024-annual-report-and-10-k.pdf</t>
+          <t>53_puma-annual-report-2024-en-final.pdf</t>
         </is>
       </c>
       <c r="D224" t="b">
@@ -4227,11 +4231,11 @@
         <v>1</v>
       </c>
       <c r="B225" t="n">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>250_250916---Notice-of-Annual-General-Meeting-2025.pdf</t>
+          <t>132_REA2023_Ang-web.pdf</t>
         </is>
       </c>
       <c r="D225" t="b">
@@ -4244,45 +4248,45 @@
         <v>1</v>
       </c>
       <c r="B226" t="n">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>92_SPAR_IAR_2024.pdf</t>
+          <t>189_0001193125-24-092555.pdf</t>
         </is>
       </c>
       <c r="D226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B227" t="n">
-        <v>151</v>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>151_annual-report-2019.pdf</t>
-        </is>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C227" t="inlineStr"/>
       <c r="D227" t="b">
         <v>0</v>
       </c>
-      <c r="E227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Primary URL is not a valid PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="b">
         <v>1</v>
       </c>
       <c r="B228" t="n">
-        <v>36</v>
+        <v>249</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>36_eu-16677_semi_annual_report_f_0.pdf</t>
+          <t>249_InvestorDay2025.pdf</t>
         </is>
       </c>
       <c r="D228" t="b">
@@ -4292,31 +4296,31 @@
     </row>
     <row r="229">
       <c r="A229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B229" t="n">
-        <v>153</v>
-      </c>
-      <c r="C229" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>50_Annual-Report-2023.pdf</t>
+        </is>
+      </c>
       <c r="D229" t="b">
         <v>0</v>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.fma.govt.nz/assets/Reports/KiwiSaver-Annual-Report-2025.pdf'</t>
-        </is>
-      </c>
+      <c r="E229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="b">
         <v>1</v>
       </c>
       <c r="B230" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>16_annual_report2024.pdf</t>
+          <t>15_E_2024%20Annual%20Report.pdf</t>
         </is>
       </c>
       <c r="D230" t="b">
@@ -4326,35 +4330,35 @@
     </row>
     <row r="231">
       <c r="A231" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B231" t="n">
-        <v>192</v>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>192_PDJF_Aarsrapport_2023_Signed.pdf</t>
-        </is>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C231" t="inlineStr"/>
       <c r="D231" t="b">
-        <v>0</v>
-      </c>
-      <c r="E231" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.bhp.com/-/media/documents/investors/annual-reports/2019/bhpannualreport2019.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="b">
         <v>1</v>
       </c>
       <c r="B232" t="n">
-        <v>270</v>
+        <v>74</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>270_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
+          <t>74_LH-AR-2024-e.pdf</t>
         </is>
       </c>
       <c r="D232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E232" t="inlineStr"/>
     </row>
@@ -4363,11 +4367,11 @@
         <v>1</v>
       </c>
       <c r="B233" t="n">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>114_ABENA-Annual-Report-2023-2024_EN.pdf</t>
+          <t>32_gabriel_annual_report_2022-23.pdf</t>
         </is>
       </c>
       <c r="D233" t="b">
@@ -4377,46 +4381,50 @@
     </row>
     <row r="234">
       <c r="A234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B234" t="n">
-        <v>231</v>
-      </c>
-      <c r="C234" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>151_annual-report-2019.pdf</t>
+        </is>
+      </c>
       <c r="D234" t="b">
         <v>0</v>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.tesla.com/sites/default/files/downloads/TSLA-Q2-2025-Update.pdf'</t>
-        </is>
-      </c>
+      <c r="E234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B235" t="n">
-        <v>191</v>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>191_diluen_annualreport_2023_sicav.pdf</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C235" t="inlineStr"/>
       <c r="D235" t="b">
         <v>0</v>
       </c>
-      <c r="E235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.ey.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B236" t="n">
-        <v>241</v>
-      </c>
-      <c r="C236" t="inlineStr"/>
+        <v>210</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>210_Cleveland_Public_Library_2024_Cuyahoga_FINAL.pdf</t>
+        </is>
+      </c>
       <c r="D236" t="b">
         <v>0</v>
       </c>
@@ -4427,11 +4435,11 @@
         <v>1</v>
       </c>
       <c r="B237" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>133_2023-annual-report-storbrand-asa.pdf</t>
+          <t>152_Ryanair-2019-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D237" t="b">
@@ -4441,31 +4449,31 @@
     </row>
     <row r="238">
       <c r="A238" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B238" t="n">
-        <v>134</v>
-      </c>
-      <c r="C238" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>94_bsc-2024-annual-report-and-10-k.pdf</t>
+        </is>
+      </c>
       <c r="D238" t="b">
-        <v>1</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.bertelsmannn.com:443 ssl:default [[SSL: TLSV1_ALERT_INTERNAL_ERROR] tlsv1 alert internal error (_ssl.c:1082)]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="b">
         <v>1</v>
       </c>
       <c r="B239" t="n">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>211_annual-report-adidas-ar23.pdf</t>
+          <t>16_annual_report2024.pdf</t>
         </is>
       </c>
       <c r="D239" t="b">
@@ -4478,11 +4486,11 @@
         <v>1</v>
       </c>
       <c r="B240" t="n">
-        <v>251</v>
+        <v>73</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>251_Draft%20conclusions_2nd%20BTR%20LRs%20meeting_2025.pdf</t>
+          <t>73_annual-report-2024-e.pdf</t>
         </is>
       </c>
       <c r="D240" t="b">
@@ -4492,14 +4500,18 @@
     </row>
     <row r="241">
       <c r="A241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B241" t="n">
-        <v>67</v>
-      </c>
-      <c r="C241" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>131_Consolidated-Annual-Accounts-2023.pdf</t>
+        </is>
+      </c>
       <c r="D241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E241" t="inlineStr"/>
     </row>
@@ -4508,11 +4520,11 @@
         <v>1</v>
       </c>
       <c r="B242" t="n">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>172_aa-annual-report-full-2021.pdf</t>
+          <t>36_eu-16677_semi_annual_report_f_0.pdf</t>
         </is>
       </c>
       <c r="D242" t="b">
@@ -4522,95 +4534,103 @@
     </row>
     <row r="243">
       <c r="A243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B243" t="n">
-        <v>37</v>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>37_grantthornton_annual-report_2023_uk.pdf</t>
-        </is>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C243" t="inlineStr"/>
       <c r="D243" t="b">
         <v>0</v>
       </c>
-      <c r="E243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.fma.govt.nz/assets/Reports/KiwiSaver-Annual-Report-2025.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B244" t="n">
-        <v>154</v>
-      </c>
-      <c r="C244" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>92_SPAR_IAR_2024.pdf</t>
+        </is>
+      </c>
       <c r="D244" t="b">
-        <v>1</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://media.defense.gov/2024/Dec/18/2003615520/-1/-1/0/MILITARY-AND-SECURITY-DEVELOPMENTS-INVOLVING-THE-PEOPLES-REPUBLIC-OF-CHINA-2024.PDF'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B245" t="n">
-        <v>115</v>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>115_aarsregnskab_2019_engelsk_2020_ok.pdf</t>
-        </is>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="C245" t="inlineStr"/>
       <c r="D245" t="b">
         <v>0</v>
       </c>
-      <c r="E245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.tesla.com/sites/default/files/downloads/TSLA-Q2-2025-Update.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="b">
         <v>1</v>
       </c>
       <c r="B246" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>271_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
+          <t>270_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
         </is>
       </c>
       <c r="D246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B247" t="n">
-        <v>223</v>
-      </c>
-      <c r="C247" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>250_250916---Notice-of-Annual-General-Meeting-2025.pdf</t>
+        </is>
+      </c>
       <c r="D247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B248" t="n">
-        <v>28</v>
-      </c>
-      <c r="C248" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>246_SDG_India_Index_2023-24.pdf</t>
+        </is>
+      </c>
       <c r="D248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E248" t="inlineStr"/>
     </row>
@@ -4619,130 +4639,126 @@
         <v>1</v>
       </c>
       <c r="B249" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>56_VSO%20Annual%20Report%202011-12.pdf</t>
+          <t>35_Barclays-PLC-Annual-Report-2024.pdf</t>
         </is>
       </c>
       <c r="D249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B250" t="n">
-        <v>232</v>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>232_OSHA-RK-Forms-Package.pdf</t>
-        </is>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B251" t="n">
-        <v>193</v>
-      </c>
-      <c r="C251" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>114_ABENA-Annual-Report-2023-2024_EN.pdf</t>
+        </is>
+      </c>
       <c r="D251" t="b">
-        <v>1</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Secondary URL is not a valid PDF.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="b">
         <v>1</v>
       </c>
       <c r="B252" t="n">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>131_Consolidated-Annual-Accounts-2023.pdf</t>
+          <t>192_PDJF_Aarsrapport_2023_Signed.pdf</t>
         </is>
       </c>
       <c r="D252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B253" t="n">
-        <v>213</v>
-      </c>
-      <c r="C253" t="inlineStr"/>
+        <v>251</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>251_Draft%20conclusions_2nd%20BTR%20LRs%20meeting_2025.pdf</t>
+        </is>
+      </c>
       <c r="D253" t="b">
         <v>0</v>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://pka.dk/globalassets/4-this-is-pka/annual-report/2023/annual-report-2023-pka-pension.pdf'</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B254" t="n">
-        <v>252</v>
-      </c>
-      <c r="C254" t="inlineStr"/>
+        <v>191</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>191_diluen_annualreport_2023_sicav.pdf</t>
+        </is>
+      </c>
       <c r="D254" t="b">
         <v>0</v>
       </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.bls.gov/news.release/pdf/cpi.pdf'</t>
-        </is>
-      </c>
+      <c r="E254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B255" t="n">
-        <v>96</v>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>96_ecit-annual-report-2023-62971.pdf</t>
-        </is>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C255" t="inlineStr"/>
       <c r="D255" t="b">
-        <v>0</v>
-      </c>
-      <c r="E255" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.bertelsmannn.com:443 ssl:default [[SSL: TLSV1_ALERT_INTERNAL_ERROR] tlsv1 alert internal error (_ssl.c:1082)]</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="b">
         <v>1</v>
       </c>
       <c r="B256" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>76_eurofins-scientific-2024-annual-report.pdf</t>
+          <t>56_VSO%20Annual%20Report%202011-12.pdf</t>
         </is>
       </c>
       <c r="D256" t="b">
@@ -4755,11 +4771,11 @@
         <v>1</v>
       </c>
       <c r="B257" t="n">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>75_carlsberg-group-2023-annual-report.pdf</t>
+          <t>17_novo-nordisk-annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D257" t="b">
@@ -4769,31 +4785,31 @@
     </row>
     <row r="258">
       <c r="A258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B258" t="n">
-        <v>57</v>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>57_annual-report-2024.pdf</t>
-        </is>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="b">
         <v>1</v>
       </c>
-      <c r="E258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.pepsino.com:443 ssl:default [None]</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="b">
         <v>1</v>
       </c>
       <c r="B259" t="n">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>17_novo-nordisk-annual-report-2023.pdf</t>
+          <t>95_niras_annual-report_2023.pdf</t>
         </is>
       </c>
       <c r="D259" t="b">
@@ -4806,11 +4822,11 @@
         <v>1</v>
       </c>
       <c r="B260" t="n">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>95_niras_annual-report_2023.pdf</t>
+          <t>172_aa-annual-report-full-2021.pdf</t>
         </is>
       </c>
       <c r="D260" t="b">
@@ -4820,35 +4836,27 @@
     </row>
     <row r="261">
       <c r="A261" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B261" t="n">
-        <v>15</v>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>15_E_2024%20Annual%20Report.pdf</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C261" t="inlineStr"/>
       <c r="D261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B262" t="n">
-        <v>93</v>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>93_2024-Annual_Report.pdf</t>
-        </is>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C262" t="inlineStr"/>
       <c r="D262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E262" t="inlineStr"/>
     </row>
@@ -4857,15 +4865,15 @@
         <v>1</v>
       </c>
       <c r="B263" t="n">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>173_kerry-group-annual-report-2023.pdf</t>
+          <t>133_2023-annual-report-storbrand-asa.pdf</t>
         </is>
       </c>
       <c r="D263" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E263" t="inlineStr"/>
     </row>
@@ -4874,11 +4882,11 @@
         <v>1</v>
       </c>
       <c r="B264" t="n">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>174_Bank-of-Ghana-2023-Annual-Report-and-Financial-Statements.pdf</t>
+          <t>211_annual-report-adidas-ar23.pdf</t>
         </is>
       </c>
       <c r="D264" t="b">
@@ -4891,15 +4899,15 @@
         <v>1</v>
       </c>
       <c r="B265" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>135_currys-annual-report-2023-24-web.pdf</t>
+          <t>173_kerry-group-annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D265" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E265" t="inlineStr"/>
     </row>
@@ -4908,11 +4916,11 @@
         <v>1</v>
       </c>
       <c r="B266" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>18_annual_report_2024_en.pdf</t>
+          <t>75_carlsberg-group-2023-annual-report.pdf</t>
         </is>
       </c>
       <c r="D266" t="b">
@@ -4925,11 +4933,11 @@
         <v>1</v>
       </c>
       <c r="B267" t="n">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>149_ia-2020-annual-report-en.pdf</t>
+          <t>93_2024-Annual_Report.pdf</t>
         </is>
       </c>
       <c r="D267" t="b">
@@ -4939,18 +4947,14 @@
     </row>
     <row r="268">
       <c r="A268" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B268" t="n">
-        <v>230</v>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>230_amNsb3VkczovLzAzLzg2LzU1LzNhL2E2L2FhNDQtNDIyNi05MTFmLTQxYzdkYTU3ZTFmOQ.pdf</t>
-        </is>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E268" t="inlineStr"/>
     </row>
@@ -4959,11 +4963,11 @@
         <v>1</v>
       </c>
       <c r="B269" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>210_Cleveland_Public_Library_2024_Cuyahoga_FINAL.pdf</t>
+          <t>230_amNsb3VkczovLzAzLzg2LzU1LzNhL2E2L2FhNDQtNDIyNi05MTFmLTQxYzdkYTU3ZTFmOQ.pdf</t>
         </is>
       </c>
       <c r="D269" t="b">
@@ -4973,12 +4977,16 @@
     </row>
     <row r="270">
       <c r="A270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B270" t="n">
-        <v>51</v>
-      </c>
-      <c r="C270" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>149_ia-2020-annual-report-en.pdf</t>
+        </is>
+      </c>
       <c r="D270" t="b">
         <v>1</v>
       </c>
@@ -4989,17 +4997,13 @@
         <v>0</v>
       </c>
       <c r="B271" t="n">
-        <v>212</v>
+        <v>51</v>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="b">
         <v>1</v>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.pepsino.com:443 ssl:default [The semaphore timeout period has expired]</t>
-        </is>
-      </c>
+      <c r="E271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="b">

--- a/CLI/download_report.xlsx
+++ b/CLI/download_report.xlsx
@@ -448,7 +448,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="b">
@@ -456,7 +456,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://media.defense.gov/2024/Dec/18/2003615520/-1/-1/0/MILITARY-AND-SECURITY-DEVELOPMENTS-INVOLVING-THE-PEOPLES-REPUBLIC-OF-CHINA-2024.PDF'</t>
+          <t>Cannot connect to host uploads.vw-mms.de:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="b">
@@ -473,7 +473,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>404, message='Not Found', url='https://pka.dk/globalassets/4-this-is-pka/annual-report/2023/annual-report-2023-pka-pension.pdf'</t>
+          <t>404, message='Not Found', url='https://www.statestreet.com/web/about/our-story/annual-report/documents/ssc-annual-report-2024.pdf'</t>
         </is>
       </c>
     </row>
@@ -482,11 +482,11 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>271</v>
+        <v>156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>271_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
+          <t>156_Annual%20Report%202021.pdf</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -496,133 +496,133 @@
     </row>
     <row r="5">
       <c r="A5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>252</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>194</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>194_Tusla_-_Annual_Report_and_Financial_Statements_2023.pdf</t>
+        </is>
+      </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.bls.gov/news.release/pdf/cpi.pdf'</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>116</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>253</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>253_BUP%20Annual%20Report%202024.pdf</t>
+        </is>
+      </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.statestreet.com/web/about/our-story/annual-report/documents/ssc-annual-report-2024.pdf'</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>136_1fff6f59-551f-4fe0-bca9-74bfc9a56aeb.pdf</t>
+        </is>
+      </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Cannot connect to host uploads.vw-mms.de:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>38_NMG2015AnnualReport.pdf</t>
+        </is>
+      </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Secondary URL is not a valid PDF.</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
         <v>175</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>175_ATA-2025-Unclassified-Report.pdf</t>
+        </is>
+      </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.dni.gov/files/ODNI/documents/assessments/ATA-2025-Unclassified-Report.pdf'</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>136</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20_relx-2024-annual-report.pdf</t>
+        </is>
+      </c>
       <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://investor.gm.com/static-files/1fff6f59-551f-4fe0-bca9-74bfc9a56aeb'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>214</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>117</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>117_2023-annual-report.pdf</t>
+        </is>
+      </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.tescoplc.com/media/u1wlq2qf/tesco-plc-annual-report-2023.pdf'</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="b">
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>76_eurofins-scientific-2024-annual-report.pdf</t>
+          <t>137_2024-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -652,15 +652,15 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>37_grantthornton_annual-report_2023_uk.pdf</t>
+          <t>97_kerry-group-annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr"/>
     </row>
@@ -669,45 +669,45 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>57</v>
+        <v>176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>57_annual-report-2024.pdf</t>
+          <t>176_CIRO-Annual-Report-2024-2025-EN.pdf</t>
         </is>
       </c>
       <c r="D15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>194</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>194_Tusla_-_Annual_Report_and_Financial_Statements_2023.pdf</t>
-        </is>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.sampension.dk/media/cce8d8d6-4bd0-4483-a862-c92c6cb7154c/zPZytg/PDF%20dokumenter/%C3%85rsrapporter/Annual%20report%202023%20SP.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="b">
         <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>38_NMG2015AnnualReport.pdf</t>
+          <t>1_novo-nordisk-annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -720,11 +720,11 @@
         <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>156_Annual%20Report%202021.pdf</t>
+          <t>254_steo_full.pdf</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -737,15 +737,15 @@
         <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>232_OSHA-RK-Forms-Package.pdf</t>
+          <t>40_novo-holdings-2023-performance-report.pdf</t>
         </is>
       </c>
       <c r="D19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
@@ -754,11 +754,11 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>253_BUP%20Annual%20Report%202024.pdf</t>
+          <t>215_Annual%20report%202023.pdf</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -771,11 +771,11 @@
         <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>117_2023-annual-report.pdf</t>
+          <t>155_gabriel_annual_report_2023-24.pdf</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -785,31 +785,31 @@
     </row>
     <row r="22">
       <c r="A22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>215</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>118</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>118_annual_report_2023.pdf</t>
+        </is>
+      </c>
       <c r="D22" t="b">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://investor-en.tcmgroup.dk/system/files-encrypted/nasdaq_kms/assets/2024/03/13/9-54-17/Annual%20report%202023.pdf'</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="b">
         <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>115_aarsregnskab_2019_engelsk_2020_ok.pdf</t>
+          <t>216_IAP-Annual-Report-2024-2025-EN.pdf</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -839,11 +839,11 @@
         <v>1</v>
       </c>
       <c r="B25" t="n">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>137_2024-Annual-Report.pdf</t>
+          <t>79_Annual-Report-2024.pdf</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -856,11 +856,11 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20_relx-2024-annual-report.pdf</t>
+          <t>60_infosys-ar-25.pdf</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -873,11 +873,11 @@
         <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>195_Beiersdorf-annual-report-2023-en.pdf</t>
+          <t>77_Annual%20report%202024.pdf</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -890,11 +890,11 @@
         <v>1</v>
       </c>
       <c r="B28" t="n">
-        <v>176</v>
+        <v>98</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>176_CIRO-Annual-Report-2024-2025-EN.pdf</t>
+          <t>98_olam_annual_report_2024.pdf</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -904,99 +904,99 @@
     </row>
     <row r="29">
       <c r="A29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>79</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>79_Annual-Report-2024.pdf</t>
-        </is>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.eif.org/files/records/eif-annual-report-2023.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>196</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+        <v>255</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>255_calls_to_action_english2.pdf</t>
+        </is>
+      </c>
       <c r="D30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.sampension.dk/media/cce8d8d6-4bd0-4483-a862-c92c6cb7154c/zPZytg/PDF%20dokumenter/%C3%85rsrapporter/Annual%20report%202023%20SP.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="b">
         <v>1</v>
       </c>
       <c r="B31" t="n">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>174_Bank-of-Ghana-2023-Annual-Report-and-Financial-Statements.pdf</t>
+          <t>233_GLEN-2023-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" t="n">
-        <v>40</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>40_novo-holdings-2023-performance-report.pdf</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="b">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://pka.dk/globalassets/4-this-is-pka/annual-report/2023/annual-report-2023-pharmaconomists.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="n">
-        <v>60</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
+        <v>99</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>99_annualreport2022.pdf</t>
+        </is>
+      </c>
       <c r="D33" t="b">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.infosys.com/investors/reports-filings/annual-report/annual/documents/infosys-ar-25.pdf'</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="b">
         <v>1</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1_novo-nordisk-annual-report-2024.pdf</t>
+          <t>41_2023-03-02_gubra-annual_report_2022_final.pdf</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -1009,11 +1009,11 @@
         <v>1</v>
       </c>
       <c r="B35" t="n">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>234_echapter.pdf</t>
+          <t>80_MM_Annual_Report_2024.pdf</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -1026,11 +1026,11 @@
         <v>1</v>
       </c>
       <c r="B36" t="n">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>96_ecit-annual-report-2023-62971.pdf</t>
+          <t>217_via-annual-report-2021-EN.pdf</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -1040,48 +1040,48 @@
     </row>
     <row r="37">
       <c r="A37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" t="n">
-        <v>216</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>216_IAP-Annual-Report-2024-2025-EN.pdf</t>
-        </is>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="b">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://www.aig.com/content/dam/aig/america-canada/us/documents/investor-relations/annual-report/aig-2023-annual-report.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" t="n">
-        <v>233</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>233_GLEN-2023-Annual-Report.pdf</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.cbs.dk:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="b">
         <v>1</v>
       </c>
       <c r="B39" t="n">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>235_dk-KPMG-annual-report-2021.pdf</t>
+          <t>178_M-and-S-2023-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -1094,15 +1094,15 @@
         <v>1</v>
       </c>
       <c r="B40" t="n">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>97_kerry-group-annual-report-2024.pdf</t>
+          <t>236_IPCC_AR6_SYR_LongerReport.pdf</t>
         </is>
       </c>
       <c r="D40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr"/>
     </row>
@@ -1111,11 +1111,11 @@
         <v>1</v>
       </c>
       <c r="B41" t="n">
-        <v>118</v>
+        <v>177</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>118_annual_report_2023.pdf</t>
+          <t>177_lewis-iar-2025.pdf</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -1125,31 +1125,31 @@
     </row>
     <row r="42">
       <c r="A42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="n">
-        <v>119</v>
-      </c>
-      <c r="C42" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>22_DHL-Group-2024-Annual-Report.pdf</t>
+        </is>
+      </c>
       <c r="D42" t="b">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.eif.org/files/records/eif-annual-report-2023.pdf'</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="b">
         <v>1</v>
       </c>
       <c r="B43" t="n">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>80_MM_Annual_Report_2024.pdf</t>
+          <t>138_mondi-group-integrated-report-and-financial-statements-2023.pdf</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -1159,31 +1159,31 @@
     </row>
     <row r="44">
       <c r="A44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="n">
-        <v>41</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>41_2023-03-02_gubra-annual_report_2022_final.pdf</t>
-        </is>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.nato.int/nato_static_fl2014/assets/pdf/2024/3/pdf/sgar23-en.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="b">
         <v>1</v>
       </c>
       <c r="B45" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>255_calls_to_action_english2.pdf</t>
+          <t>256_i990.pdf</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -1193,31 +1193,31 @@
     </row>
     <row r="46">
       <c r="A46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="n">
-        <v>100</v>
-      </c>
-      <c r="C46" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>120_basic-understanding-of-a-companys-financials.pdf</t>
+        </is>
+      </c>
       <c r="D46" t="b">
         <v>0</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://pka.dk/globalassets/4-this-is-pka/annual-report/2023/annual-report-2023-pharmaconomists.pdf'</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="b">
         <v>1</v>
       </c>
       <c r="B47" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>77_Annual%20report%202024.pdf</t>
+          <t>61_loreal2024annualreport.pdf</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -1230,11 +1230,11 @@
         <v>1</v>
       </c>
       <c r="B48" t="n">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>138_mondi-group-integrated-report-and-financial-statements-2023.pdf</t>
+          <t>159_annual-report-2023-24.pdf</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -1247,11 +1247,11 @@
         <v>1</v>
       </c>
       <c r="B49" t="n">
-        <v>236</v>
+        <v>23</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>236_IPCC_AR6_SYR_LongerReport.pdf</t>
+          <t>23_Annual-Report-2024.pdf</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -1264,11 +1264,11 @@
         <v>1</v>
       </c>
       <c r="B50" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>217_via-annual-report-2021-EN.pdf</t>
+          <t>214_tesco-plc-annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -1281,45 +1281,45 @@
         <v>1</v>
       </c>
       <c r="B51" t="n">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>78_GLEN-2024-Annual-Report.pdf</t>
+          <t>237_hgt-interim-report-and-accounts-2025.pdf</t>
         </is>
       </c>
       <c r="D51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
-      </c>
-      <c r="C52" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>81_Beiersdorf-Annual-Report-2024.pdf</t>
+        </is>
+      </c>
       <c r="D52" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.cbs.dk:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="b">
         <v>1</v>
       </c>
       <c r="B53" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>61_loreal2024annualreport.pdf</t>
+          <t>62_%E8%8B%B1%E6%96%87.pdf</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -1329,82 +1329,82 @@
     </row>
     <row r="54">
       <c r="A54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="n">
-        <v>256</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>256_i990.pdf</t>
-        </is>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.mospi.gov.in:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B55" t="n">
-        <v>120</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
+        <v>101</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>101_burberry-annual-report-and-accounts-2023-24.pdf</t>
+        </is>
+      </c>
       <c r="D55" t="b">
         <v>0</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.pwc.com/jm/en/research-publications/pdf/basic-understanding-of-a-companys-financials.pdf'</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B56" t="n">
-        <v>198</v>
-      </c>
-      <c r="C56" t="inlineStr"/>
+        <v>218</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>218_f940.pdf</t>
+        </is>
+      </c>
       <c r="D56" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.nato.int/nato_static_fl2014/assets/pdf/2024/3/pdf/sgar23-en.pdf'</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B57" t="n">
-        <v>197</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>197_WEF_Future_of_Jobs_Report_2025.pdf</t>
-        </is>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.epfo.gov.in/site_docs/Annual_Report/Annual_Report_2022-23.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="b">
         <v>1</v>
       </c>
       <c r="B58" t="n">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>81_Beiersdorf-Annual-Report-2024.pdf</t>
+          <t>160_2020-annual-report.pdf</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -1414,31 +1414,31 @@
     </row>
     <row r="59">
       <c r="A59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" t="n">
-        <v>62</v>
-      </c>
-      <c r="C59" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>58_annual-report-2024.pdf</t>
+        </is>
+      </c>
       <c r="D59" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://ir.mi.com/system/files-encrypted/nasdaq_kms/assets/2025/04/24/5-27-15/%E8%8B%B1%E6%96%87.pdf'</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="b">
         <v>1</v>
       </c>
       <c r="B60" t="n">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>178_M-and-S-2023-Annual-Report.pdf</t>
+          <t>59_annualreports-2021_en.pdf</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -1448,48 +1448,48 @@
     </row>
     <row r="61">
       <c r="A61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" t="n">
-        <v>101</v>
-      </c>
-      <c r="C61" t="inlineStr"/>
+        <v>235</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>235_dk-KPMG-annual-report-2021.pdf</t>
+        </is>
+      </c>
       <c r="D61" t="b">
         <v>0</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.burberryplc.com/content/dam/burberryplc/corporate/2024-updates/burberry-annual-report-and-accounts-2023-24.pdf'</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B62" t="n">
-        <v>159</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>159_annual-report-2023-24.pdf</t>
-        </is>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="b">
         <v>0</v>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Primary URL is not a valid PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="b">
         <v>1</v>
       </c>
       <c r="B63" t="n">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>58_annual-report-2024.pdf</t>
+          <t>141_Annual_Report_2021.pdf</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -1502,11 +1502,11 @@
         <v>1</v>
       </c>
       <c r="B64" t="n">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>99_annualreport2022.pdf</t>
+          <t>195_Beiersdorf-annual-report-2023-en.pdf</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -1519,45 +1519,45 @@
         <v>1</v>
       </c>
       <c r="B65" t="n">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>157_Inditex_Group_Annual_Accounts_2023.pdf</t>
+          <t>258_Republic_Act_No_6713.pdf</t>
         </is>
       </c>
       <c r="D65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B66" t="n">
-        <v>257</v>
-      </c>
-      <c r="C66" t="inlineStr"/>
+        <v>180</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>180_Annual-report-2023.pdf</t>
+        </is>
+      </c>
       <c r="D66" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.mospi.gov.in:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="b">
         <v>1</v>
       </c>
       <c r="B67" t="n">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>98_olam_annual_report_2024.pdf</t>
+          <t>157_Inditex_Group_Annual_Accounts_2023.pdf</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -1567,48 +1567,48 @@
     </row>
     <row r="68">
       <c r="A68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B68" t="n">
-        <v>237</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>237_hgt-interim-report-and-accounts-2025.pdf</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="b">
-        <v>0</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://eifo.dk/media/f23eicl4/eifo-annual-report-2024.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B69" t="n">
-        <v>155</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>155_gabriel_annual_report_2023-24.pdf</t>
-        </is>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="b">
         <v>0</v>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.bp.com/content/dam/bp/business-sites/en/global/corporate/pdfs/investors/bp-annual-report-and-form-20f-2019.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="b">
         <v>1</v>
       </c>
       <c r="B70" t="n">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>135_currys-annual-report-2023-24-web.pdf</t>
+          <t>83_nib-annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -1618,31 +1618,31 @@
     </row>
     <row r="71">
       <c r="A71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B71" t="n">
-        <v>82</v>
-      </c>
-      <c r="C71" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>43_danske-bank---annual-report-2023.pdf</t>
+        </is>
+      </c>
       <c r="D71" t="b">
         <v>0</v>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.fidelityinternational.com/legal/documents/FF/en/ar.ff.en.xx.pdf'</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="b">
         <v>1</v>
       </c>
       <c r="B72" t="n">
-        <v>218</v>
+        <v>102</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>218_f940.pdf</t>
+          <t>102_Carnival-Corporation-plc-2024-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -1655,15 +1655,15 @@
         <v>1</v>
       </c>
       <c r="B73" t="n">
-        <v>254</v>
+        <v>179</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>254_steo_full.pdf</t>
+          <t>179_Blender-Foundation-Annual-Report-2024.pdf</t>
         </is>
       </c>
       <c r="D73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr"/>
     </row>
@@ -1672,83 +1672,83 @@
         <v>1</v>
       </c>
       <c r="B74" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>23_Annual-Report-2024.pdf</t>
+          <t>54_annual-report-2018.pdf</t>
         </is>
       </c>
       <c r="D74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B75" t="n">
-        <v>139</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>139_aig-2023-annual-report.pdf</t>
-        </is>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="b">
         <v>0</v>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.sama.gov.sa:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B76" t="n">
-        <v>199</v>
-      </c>
-      <c r="C76" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>78_GLEN-2024-Annual-Report.pdf</t>
+        </is>
+      </c>
       <c r="D76" t="b">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.epfo.gov.in/site_docs/Annual_Report/Annual_Report_2022-23.pdf'</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B77" t="n">
-        <v>63</v>
-      </c>
-      <c r="C77" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>122_Annual-Report-22.pdf</t>
+        </is>
+      </c>
       <c r="D77" t="b">
         <v>0</v>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Primary URL is not a valid PDF.</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="b">
         <v>1</v>
       </c>
       <c r="B78" t="n">
-        <v>141</v>
+        <v>239</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>141_Annual_Report_2021.pdf</t>
+          <t>239_IntegratedAnnualReport2024_Unofficial%20Version_Unaudited_0.pdf</t>
         </is>
       </c>
       <c r="D78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr"/>
     </row>
@@ -1757,15 +1757,15 @@
         <v>1</v>
       </c>
       <c r="B79" t="n">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>54_annual-report-2018.pdf</t>
+          <t>140_2637721.pdf</t>
         </is>
       </c>
       <c r="D79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="inlineStr"/>
     </row>
@@ -1774,15 +1774,15 @@
         <v>1</v>
       </c>
       <c r="B80" t="n">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>160_2020-annual-report.pdf</t>
+          <t>4_annual-report-nordea-bank-abp-2024-0.pdf</t>
         </is>
       </c>
       <c r="D80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr"/>
     </row>
@@ -1791,11 +1791,11 @@
         <v>1</v>
       </c>
       <c r="B81" t="n">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>180_Annual-report-2023.pdf</t>
+          <t>259_2025_ASR_PENN.pdf</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -1808,11 +1808,11 @@
         <v>1</v>
       </c>
       <c r="B82" t="n">
-        <v>42</v>
+        <v>234</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>42_250219-annual-report-and-accounts-2024.pdf</t>
+          <t>234_echapter.pdf</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -1825,49 +1825,49 @@
         <v>1</v>
       </c>
       <c r="B83" t="n">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>258_Republic_Act_No_6713.pdf</t>
+          <t>220_annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B84" t="n">
-        <v>161</v>
-      </c>
-      <c r="C84" t="inlineStr"/>
+        <v>197</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>197_WEF_Future_of_Jobs_Report_2025.pdf</t>
+        </is>
+      </c>
       <c r="D84" t="b">
-        <v>0</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.bp.com/content/dam/bp/business-sites/en/global/corporate/pdfs/investors/bp-annual-report-and-form-20f-2019.pdf'</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="b">
         <v>1</v>
       </c>
       <c r="B85" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>140_2637721.pdf</t>
+          <t>121_Annual-Report-2022.pdf</t>
         </is>
       </c>
       <c r="D85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="inlineStr"/>
     </row>
@@ -1876,11 +1876,11 @@
         <v>1</v>
       </c>
       <c r="B86" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>43_danske-bank---annual-report-2023.pdf</t>
+          <t>42_250219-annual-report-and-accounts-2024.pdf</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -1890,31 +1890,31 @@
     </row>
     <row r="87">
       <c r="A87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
-      </c>
-      <c r="C87" t="inlineStr"/>
+        <v>238</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>238_jpm-us-smaller-companies-web-hyr-2025.pdf</t>
+        </is>
+      </c>
       <c r="D87" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://eifo.dk/media/f23eicl4/eifo-annual-report-2024.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="b">
         <v>1</v>
       </c>
       <c r="B88" t="n">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>158_Annual-Report-2020_ENG1.pdf</t>
+          <t>201_s72618-4826123-177031.pdf</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -1927,11 +1927,11 @@
         <v>1</v>
       </c>
       <c r="B89" t="n">
-        <v>4</v>
+        <v>240</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>4_annual-report-nordea-bank-abp-2024-0.pdf</t>
+          <t>240_2025-09-16-bernstein-ann.pdf</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -1944,11 +1944,11 @@
         <v>1</v>
       </c>
       <c r="B90" t="n">
-        <v>59</v>
+        <v>162</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>59_annualreports-2021_en.pdf</t>
+          <t>162_2024-financial-statements-en.pdf</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -1961,45 +1961,45 @@
         <v>1</v>
       </c>
       <c r="B91" t="n">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>102_Carnival-Corporation-plc-2024-Annual-Report.pdf</t>
+          <t>158_Annual-Report-2020_ENG1.pdf</t>
         </is>
       </c>
       <c r="D91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B92" t="n">
-        <v>142</v>
-      </c>
-      <c r="C92" t="inlineStr"/>
+        <v>143</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>143_2024-annual-report.pdf</t>
+        </is>
+      </c>
       <c r="D92" t="b">
         <v>0</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.sama.gov.sa:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="b">
         <v>1</v>
       </c>
       <c r="B93" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>122_Annual-Report-22.pdf</t>
+          <t>123_ar-2024.pdf</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -2012,15 +2012,15 @@
         <v>0</v>
       </c>
       <c r="B94" t="n">
-        <v>6</v>
+        <v>221</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://investor.maersk.com/static-files/31bf05a1-6f0c-4fbd-a3c7-3f58e044f668'</t>
+          <t>404, message='Not Found', url='https://www.bseindia.com/xml-data/corpfiling/AttachLive/7872a5ce-3f97-4e1b-a8f7-e5801677507c.pdf'</t>
         </is>
       </c>
     </row>
@@ -2029,11 +2029,11 @@
         <v>1</v>
       </c>
       <c r="B95" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>220_annual-report-2023.pdf</t>
+          <t>219_Digital_News-Report_2025.pdf</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -2046,11 +2046,11 @@
         <v>1</v>
       </c>
       <c r="B96" t="n">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>259_2025_ASR_PENN.pdf</t>
+          <t>82_ar.pdf</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -2063,11 +2063,11 @@
         <v>1</v>
       </c>
       <c r="B97" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>200_250916---Annual-Report-2025.pdf</t>
+          <t>260_SBCL_17092025111423_SBCL_Proceednigupdated.pdf</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -2077,48 +2077,48 @@
     </row>
     <row r="98">
       <c r="A98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B98" t="n">
-        <v>239</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>239_IntegratedAnnualReport2024_Unofficial%20Version_Unaudited_0.pdf</t>
-        </is>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="b">
         <v>0</v>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://www.reckitt.com/media/5qbh523b/annual-report-2022.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B99" t="n">
-        <v>201</v>
-      </c>
-      <c r="C99" t="inlineStr"/>
+        <v>181</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>181_annual-report-2023.pdf</t>
+        </is>
+      </c>
       <c r="D99" t="b">
         <v>0</v>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.sec.gov/comments/s7-26-18/s72618-4826123-177031.pdf'</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="b">
         <v>1</v>
       </c>
       <c r="B100" t="n">
-        <v>162</v>
+        <v>45</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>162_2024-financial-statements-en.pdf</t>
+          <t>45_annual_report_2020.pdf</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -2131,11 +2131,11 @@
         <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>240_2025-09-16-bernstein-ann.pdf</t>
+          <t>7_r1200appendix_d.pdf</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -2165,45 +2165,45 @@
         <v>1</v>
       </c>
       <c r="B103" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>84_dk-KPMG-Annual-report%202024_Digital-final.pdf</t>
+          <t>44_annual-report-nordea-bank-abp-2023.pdf</t>
         </is>
       </c>
       <c r="D103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B104" t="n">
-        <v>123</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>123_ar-2024.pdf</t>
-        </is>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="b">
         <v>0</v>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.experianplc.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="b">
         <v>1</v>
       </c>
       <c r="B105" t="n">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>143_2024-annual-report.pdf</t>
+          <t>26_250219-annual-report-and-accounts-2024.pdf</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -2216,11 +2216,11 @@
         <v>1</v>
       </c>
       <c r="B106" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>104_PhilipsFullAnnualReport2024-English.pdf</t>
+          <t>105_Annual_Report_AU_2021.pdf</t>
         </is>
       </c>
       <c r="D106" t="b">
@@ -2233,15 +2233,15 @@
         <v>1</v>
       </c>
       <c r="B107" t="n">
-        <v>44</v>
+        <v>163</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>44_annual-report-nordea-bank-abp-2023.pdf</t>
+          <t>163_dwp_annual_report_and_accounts_2023_2024.pdf</t>
         </is>
       </c>
       <c r="D107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="inlineStr"/>
     </row>
@@ -2250,11 +2250,11 @@
         <v>1</v>
       </c>
       <c r="B108" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>260_SBCL_17092025111423_SBCL_Proceednigupdated.pdf</t>
+          <t>200_250916---Annual-Report-2025.pdf</t>
         </is>
       </c>
       <c r="D108" t="b">
@@ -2267,11 +2267,11 @@
         <v>1</v>
       </c>
       <c r="B109" t="n">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>21_Inditex_Group_Annual_Report_2024.pdf</t>
+          <t>261_gc69_schedule_monday.pdf</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -2281,35 +2281,35 @@
     </row>
     <row r="110">
       <c r="A110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B110" t="n">
-        <v>221</v>
-      </c>
-      <c r="C110" t="inlineStr"/>
+        <v>104</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>104_PhilipsFullAnnualReport2024-English.pdf</t>
+        </is>
+      </c>
       <c r="D110" t="b">
         <v>0</v>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.bseindia.com/xml-data/corpfiling/AttachLive/7872a5ce-3f97-4e1b-a8f7-e5801677507c.pdf'</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="b">
         <v>1</v>
       </c>
       <c r="B111" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>45_annual_report_2020.pdf</t>
+          <t>64_annualreport-2024.pdf</t>
         </is>
       </c>
       <c r="D111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="inlineStr"/>
     </row>
@@ -2318,11 +2318,11 @@
         <v>1</v>
       </c>
       <c r="B112" t="n">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>121_Annual-Report-2022.pdf</t>
+          <t>66_sw-2024-annual-report.pdf</t>
         </is>
       </c>
       <c r="D112" t="b">
@@ -2335,15 +2335,15 @@
         <v>1</v>
       </c>
       <c r="B113" t="n">
-        <v>219</v>
+        <v>46</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>219_Digital_News-Report_2025.pdf</t>
+          <t>46_guide-to-understanding-annual-reporting.pdf</t>
         </is>
       </c>
       <c r="D113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" t="inlineStr"/>
     </row>
@@ -2352,62 +2352,62 @@
         <v>1</v>
       </c>
       <c r="B114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>7_r1200appendix_d.pdf</t>
+          <t>6_31bf05a1-6f0c-4fbd-a3c7-3f58e044f668.pdf</t>
         </is>
       </c>
       <c r="D114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B115" t="n">
-        <v>124</v>
-      </c>
-      <c r="C115" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>85_ihg-ar-2024.pdf</t>
+        </is>
+      </c>
       <c r="D115" t="b">
         <v>0</v>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.reckitt.com/media/5qbh523b/annual-report-2022.pdf'</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B116" t="n">
-        <v>181</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>181_annual-report-2023.pdf</t>
-        </is>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="b">
         <v>0</v>
       </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>403, message='Forbidden', url='https://www.accc.gov.au/system/files/accc-aer-audit-risk-committee-charter-august-2025.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="b">
         <v>1</v>
       </c>
       <c r="B117" t="n">
-        <v>24</v>
+        <v>203</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>24_heineken_n_v_annual_report_2024_final_20feb2025.pdf</t>
+          <t>203_38c6e738-8eda-11f0-a482-6e440358bbe4.pdf</t>
         </is>
       </c>
       <c r="D117" t="b">
@@ -2417,31 +2417,31 @@
     </row>
     <row r="118">
       <c r="A118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B118" t="n">
-        <v>144</v>
-      </c>
-      <c r="C118" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>24_heineken_n_v_annual_report_2024_final_20feb2025.pdf</t>
+        </is>
+      </c>
       <c r="D118" t="b">
         <v>0</v>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.experianplc.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="b">
         <v>1</v>
       </c>
       <c r="B119" t="n">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>26_250219-annual-report-and-accounts-2024.pdf</t>
+          <t>202_Woolworths%20Group%20Annual%20Report%202025%20.pdf</t>
         </is>
       </c>
       <c r="D119" t="b">
@@ -2451,31 +2451,31 @@
     </row>
     <row r="120">
       <c r="A120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B120" t="n">
-        <v>177</v>
-      </c>
-      <c r="C120" t="inlineStr"/>
+        <v>183</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>183_259396.pdf</t>
+        </is>
+      </c>
       <c r="D120" t="b">
         <v>0</v>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Cannot connect to host lewisgroup.co.za:443 ssl:default [The semaphore timeout period has expired]</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="b">
         <v>1</v>
       </c>
       <c r="B121" t="n">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>83_nib-annual-report-2024.pdf</t>
+          <t>125_annual-reports-and-accounts-2021.pdf</t>
         </is>
       </c>
       <c r="D121" t="b">
@@ -2485,35 +2485,35 @@
     </row>
     <row r="122">
       <c r="A122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B122" t="n">
-        <v>105</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>105_Annual_Report_AU_2021.pdf</t>
-        </is>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="b">
         <v>0</v>
       </c>
-      <c r="E122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Primary URL is not a valid PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="b">
         <v>1</v>
       </c>
       <c r="B123" t="n">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>66_sw-2024-annual-report.pdf</t>
+          <t>182_kingfisher-annual-report-202324-pdf.pdf</t>
         </is>
       </c>
       <c r="D123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="inlineStr"/>
     </row>
@@ -2522,15 +2522,15 @@
         <v>1</v>
       </c>
       <c r="B124" t="n">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>179_Blender-Foundation-Annual-Report-2024.pdf</t>
+          <t>145_SG-Annual-Report-on-the-work-of-the-Organization.pdf</t>
         </is>
       </c>
       <c r="D124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="inlineStr"/>
     </row>
@@ -2539,11 +2539,11 @@
         <v>1</v>
       </c>
       <c r="B125" t="n">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>261_gc69_schedule_monday.pdf</t>
+          <t>27_2024-informa-annual-report.pdf</t>
         </is>
       </c>
       <c r="D125" t="b">
@@ -2556,26 +2556,30 @@
         <v>1</v>
       </c>
       <c r="B126" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>46_guide-to-understanding-annual-reporting.pdf</t>
+          <t>21_Inditex_Group_Annual_Report_2024.pdf</t>
         </is>
       </c>
       <c r="D126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B127" t="n">
-        <v>18</v>
-      </c>
-      <c r="C127" t="inlineStr"/>
+        <v>222</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>222_MPA-2021-THEME-Report-FINAL.pdf</t>
+        </is>
+      </c>
       <c r="D127" t="b">
         <v>0</v>
       </c>
@@ -2583,65 +2587,65 @@
     </row>
     <row r="128">
       <c r="A128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B128" t="n">
-        <v>8</v>
-      </c>
-      <c r="C128" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>106_10610-001-BPTA_Best-practice-2014-15_FINAL.pdf</t>
+        </is>
+      </c>
       <c r="D128" t="b">
         <v>1</v>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.unilever.com/files/unilever-annual-report-and-accounts-2024.pdf'</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="b">
         <v>0</v>
       </c>
       <c r="B129" t="n">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.unilever.com/files/33321193-0d9a-44dd-93f8-02209fc6bd54/annual-report-and-accounts-2021.pdf'</t>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://www.bp.com/investors/results-reporting-and-presentations/archive-of-results-reports-and-presentations/2024'</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B130" t="n">
-        <v>163</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>163_dwp_annual_report_and_accounts_2023_2024.pdf</t>
-        </is>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="b">
         <v>0</v>
       </c>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://www.bdo.dk/getattachment/076aaf10-13d2-4ddb-a7e2-8147a2e2ce9a/2025-04-08_BDO-Arsrapport2023_24_ENGELSK.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="b">
         <v>1</v>
       </c>
       <c r="B131" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>85_ihg-ar-2024.pdf</t>
+          <t>84_dk-KPMG-Annual-report%202024_Digital-final.pdf</t>
         </is>
       </c>
       <c r="D131" t="b">
@@ -2654,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="n">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="b">
@@ -2662,37 +2666,37 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.accc.gov.au/system/files/accc-aer-audit-risk-committee-charter-august-2025.pdf'</t>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://investorrelations.bankofireland.com/app/uploads/BOI-Annual-Report-2020.pdf'</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B133" t="n">
-        <v>184</v>
-      </c>
-      <c r="C133" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>65_aa-annual-report-full-2024.pdf</t>
+        </is>
+      </c>
       <c r="D133" t="b">
         <v>0</v>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Primary URL is not a valid PDF.</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="b">
         <v>1</v>
       </c>
       <c r="B134" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>65_aa-annual-report-full-2024.pdf</t>
+          <t>68_202505020944401774654665_en.pdf</t>
         </is>
       </c>
       <c r="D134" t="b">
@@ -2705,11 +2709,11 @@
         <v>1</v>
       </c>
       <c r="B135" t="n">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>27_2024-informa-annual-report.pdf</t>
+          <t>243_0001140361-25-035121.pdf</t>
         </is>
       </c>
       <c r="D135" t="b">
@@ -2722,11 +2726,11 @@
         <v>1</v>
       </c>
       <c r="B136" t="n">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>182_kingfisher-annual-report-202324-pdf.pdf</t>
+          <t>262_07d4ee9c-934c-11f0-8802-ae41b78b60fd.pdf</t>
         </is>
       </c>
       <c r="D136" t="b">
@@ -2736,99 +2740,99 @@
     </row>
     <row r="137">
       <c r="A137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B137" t="n">
-        <v>145</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>145_SG-Annual-Report-on-the-work-of-the-Organization.pdf</t>
-        </is>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="b">
-        <v>0</v>
-      </c>
-      <c r="E137" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Cannot connect to host labour.gov.in:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="b">
         <v>1</v>
       </c>
       <c r="B138" t="n">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>183_259396.pdf</t>
+          <t>8_unilever-annual-report-and-accounts-2024.pdf</t>
         </is>
       </c>
       <c r="D138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B139" t="n">
-        <v>202</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>202_Woolworths%20Group%20Annual%20Report%202025%20.pdf</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="b">
-        <v>0</v>
-      </c>
-      <c r="E139" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>429, message='Too Many Requests', url='https://zerodha.com/varsity/chapter/read-annual-report-company/'</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="b">
         <v>1</v>
       </c>
       <c r="B140" t="n">
-        <v>64</v>
+        <v>224</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>64_annualreport-2024.pdf</t>
+          <t>224_annual-report-2023-24.pdf</t>
         </is>
       </c>
       <c r="D140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B141" t="n">
-        <v>204</v>
-      </c>
-      <c r="C141" t="inlineStr"/>
+        <v>164</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>164_atea-annual-report-2021.pdf</t>
+        </is>
+      </c>
       <c r="D141" t="b">
         <v>1</v>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://group.mercedes-benz.com/documents/investors/reports/annual-report/mercedes-benz/mercedes-benz-annual-report-2023-incl-combined-management-report-mbg-ag.pdf'</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="b">
         <v>1</v>
       </c>
       <c r="B142" t="n">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>203_38c6e738-8eda-11f0-a482-6e440358bbe4.pdf</t>
+          <t>166_2020ar.pdf</t>
         </is>
       </c>
       <c r="D142" t="b">
@@ -2841,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="B143" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="b">
@@ -2849,7 +2853,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Primary URL is not a valid PDF.</t>
+          <t>404, message='Not Found', url='https://www.boeing.com/content/dam/boeing/boeingdotcom/company/annual-report/2024/2024-annual-report.pdf'</t>
         </is>
       </c>
     </row>
@@ -2858,11 +2862,11 @@
         <v>1</v>
       </c>
       <c r="B144" t="n">
-        <v>243</v>
+        <v>88</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>243_0001140361-25-035121.pdf</t>
+          <t>88_statkraft-as---annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D144" t="b">
@@ -2875,11 +2879,11 @@
         <v>1</v>
       </c>
       <c r="B145" t="n">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>107_2025-04-08_BDO-Arsrapport2023_24_ENGELSK.pdf</t>
+          <t>147_inter-ikea-holding-bv-annual-report-fy24.pdf</t>
         </is>
       </c>
       <c r="D145" t="b">
@@ -2892,49 +2896,49 @@
         <v>1</v>
       </c>
       <c r="B146" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>106_10610-001-BPTA_Best-practice-2014-15_FINAL.pdf</t>
+          <t>127_daa-Annual-Report-2024-ENG-Web.pdf</t>
         </is>
       </c>
       <c r="D146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B147" t="n">
-        <v>165</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>165_richemont-fy24-annual-report-en.pdf</t>
-        </is>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="b">
-        <v>0</v>
-      </c>
-      <c r="E147" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://www.idx.co.id/Portals/0/StaticData/ListedCompanies/Corporate_Actions/New_Info_JSX/Jenis_Informasi/01_Laporan_Keuangan/04_Annual%20Report/2018/INDF/INDF_Annual%20Report_2018.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="b">
         <v>1</v>
       </c>
       <c r="B148" t="n">
-        <v>68</v>
+        <v>204</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>68_202505020944401774654665_en.pdf</t>
+          <t>204_mercedes-benz-annual-report-2023-incl-combined-management-report-mbg-ag.pdf</t>
         </is>
       </c>
       <c r="D148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" t="inlineStr"/>
     </row>
@@ -2943,11 +2947,11 @@
         <v>1</v>
       </c>
       <c r="B149" t="n">
-        <v>222</v>
+        <v>103</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>222_MPA-2021-THEME-Report-FINAL.pdf</t>
+          <t>103_Informe-anual-2024_ENG.pdf</t>
         </is>
       </c>
       <c r="D149" t="b">
@@ -2960,49 +2964,49 @@
         <v>1</v>
       </c>
       <c r="B150" t="n">
-        <v>164</v>
+        <v>67</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>164_atea-annual-report-2021.pdf</t>
+          <t>67_BMW-Group-Report-2024-en.pdf</t>
         </is>
       </c>
       <c r="D150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B151" t="n">
-        <v>10</v>
-      </c>
-      <c r="C151" t="inlineStr"/>
+        <v>108</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>108_amNsb3VkczovLzAzLzMxLzhmLzkyLzFhLzc5NTMtNDQzZS1hMmFlLTgxNWRlYWVkNGNlOQ.pdf</t>
+        </is>
+      </c>
       <c r="D151" t="b">
-        <v>1</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Secondary URL is not a valid PDF.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="b">
         <v>0</v>
       </c>
       <c r="B152" t="n">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Cannot connect to host labour.gov.in:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+          <t>Cannot connect to host en-rules.hkex.com.hk:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
         </is>
       </c>
     </row>
@@ -3011,11 +3015,11 @@
         <v>1</v>
       </c>
       <c r="B153" t="n">
-        <v>224</v>
+        <v>48</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>224_annual-report-2023-24.pdf</t>
+          <t>48_Ryanair-2023-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D153" t="b">
@@ -3028,15 +3032,15 @@
         <v>1</v>
       </c>
       <c r="B154" t="n">
-        <v>262</v>
+        <v>89</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>262_07d4ee9c-934c-11f0-8802-ae41b78b60fd.pdf</t>
+          <t>89_form_06_com_-_annual_report.pdf</t>
         </is>
       </c>
       <c r="D154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" t="inlineStr"/>
     </row>
@@ -3045,11 +3049,11 @@
         <v>1</v>
       </c>
       <c r="B155" t="n">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>146_BOI-Annual-Report-2020.pdf</t>
+          <t>49_annual-review-2024-en.pdf</t>
         </is>
       </c>
       <c r="D155" t="b">
@@ -3079,15 +3083,15 @@
         <v>1</v>
       </c>
       <c r="B157" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>166_2020ar.pdf</t>
+          <t>167_LH-AR-2021-e.pdf</t>
         </is>
       </c>
       <c r="D157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="inlineStr"/>
     </row>
@@ -3096,11 +3100,11 @@
         <v>1</v>
       </c>
       <c r="B158" t="n">
-        <v>48</v>
+        <v>206</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>48_Ryanair-2023-Annual-Report.pdf</t>
+          <t>206_full-report.pdf</t>
         </is>
       </c>
       <c r="D158" t="b">
@@ -3110,31 +3114,31 @@
     </row>
     <row r="159">
       <c r="A159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B159" t="n">
-        <v>30</v>
-      </c>
-      <c r="C159" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>186_2023-informa-annual-report.pdf</t>
+        </is>
+      </c>
       <c r="D159" t="b">
         <v>0</v>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.boeing.com/content/dam/boeing/boeingdotcom/company/annual-report/2024/2024-annual-report.pdf'</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="b">
         <v>1</v>
       </c>
       <c r="B160" t="n">
-        <v>88</v>
+        <v>244</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>88_statkraft-as---annual-report-2024.pdf</t>
+          <t>244_Annual-CSR-Report-2023-24.pdf</t>
         </is>
       </c>
       <c r="D160" t="b">
@@ -3147,11 +3151,11 @@
         <v>1</v>
       </c>
       <c r="B161" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>127_daa-Annual-Report-2024-ENG-Web.pdf</t>
+          <t>109_annual-report-2020-21.pdf</t>
         </is>
       </c>
       <c r="D161" t="b">
@@ -3164,11 +3168,11 @@
         <v>1</v>
       </c>
       <c r="B162" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>147_inter-ikea-holding-bv-annual-report-fy24.pdf</t>
+          <t>205_annual-report-2023-extract---pensiondanmark.pdf</t>
         </is>
       </c>
       <c r="D162" t="b">
@@ -3181,11 +3185,11 @@
         <v>1</v>
       </c>
       <c r="B163" t="n">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>186_2023-informa-annual-report.pdf</t>
+          <t>265_ssa-7050.pdf</t>
         </is>
       </c>
       <c r="D163" t="b">
@@ -3195,31 +3199,31 @@
     </row>
     <row r="164">
       <c r="A164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B164" t="n">
-        <v>225</v>
-      </c>
-      <c r="C164" t="inlineStr"/>
+        <v>187</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>187_annualreport-2023.pdf</t>
+        </is>
+      </c>
       <c r="D164" t="b">
         <v>0</v>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Cannot connect to host en-rules.hkex.com.hk:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="b">
         <v>1</v>
       </c>
       <c r="B165" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>49_annual-review-2024-en.pdf</t>
+          <t>69_2024-annual-report.pdf</t>
         </is>
       </c>
       <c r="D165" t="b">
@@ -3232,11 +3236,11 @@
         <v>1</v>
       </c>
       <c r="B166" t="n">
-        <v>69</v>
+        <v>226</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>69_2024-annual-report.pdf</t>
+          <t>226_240226-annual-report-and-accounts-2023.pdf</t>
         </is>
       </c>
       <c r="D166" t="b">
@@ -3246,48 +3250,48 @@
     </row>
     <row r="167">
       <c r="A167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B167" t="n">
-        <v>205</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>205_annual-report-2023-extract---pensiondanmark.pdf</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="b">
         <v>0</v>
       </c>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Cannot connect to host annualreport2024.volkswagen-group.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B168" t="n">
-        <v>128</v>
-      </c>
-      <c r="C168" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>31_tdc-net-annual-report-2023.pdf</t>
+        </is>
+      </c>
       <c r="D168" t="b">
-        <v>1</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.merckgroup.com/investors/reports-and-financials/earnings-materials/2022-q4/en/2022-Q4-Report-EN.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="b">
         <v>1</v>
       </c>
       <c r="B169" t="n">
-        <v>108</v>
+        <v>264</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>108_amNsb3VkczovLzAzLzMxLzhmLzkyLzFhLzc5NTMtNDQzZS1hMmFlLTgxNWRlYWVkNGNlOQ.pdf</t>
+          <t>264_Global-Peace-Index-2025-web.pdf</t>
         </is>
       </c>
       <c r="D169" t="b">
@@ -3300,15 +3304,15 @@
         <v>1</v>
       </c>
       <c r="B170" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>89_form_06_com_-_annual_report.pdf</t>
+          <t>70_MunichRe-Group-Annual-Report-2024-en.pdf</t>
         </is>
       </c>
       <c r="D170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E170" t="inlineStr"/>
     </row>
@@ -3317,15 +3321,15 @@
         <v>0</v>
       </c>
       <c r="B171" t="n">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.idx.co.id/Portals/0/StaticData/ListedCompanies/Corporate_Actions/New_Info_JSX/Jenis_Informasi/01_Laporan_Keuangan/04_Annual%20Report/2018/INDF/INDF_Annual%20Report_2018.pdf'</t>
+          <t>404, message='Not Found', url='https://cdn.rigsrevisionen.dk/rigsrevisionen/Media/638229369267919065/Annual-report-2022.pdf'</t>
         </is>
       </c>
     </row>
@@ -3334,11 +3338,11 @@
         <v>1</v>
       </c>
       <c r="B172" t="n">
-        <v>264</v>
+        <v>12</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>264_Global-Peace-Index-2025-web.pdf</t>
+          <t>12_annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D172" t="b">
@@ -3351,11 +3355,11 @@
         <v>1</v>
       </c>
       <c r="B173" t="n">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>109_annual-report-2020-21.pdf</t>
+          <t>11_annual-report-adidas-ar24.pdf</t>
         </is>
       </c>
       <c r="D173" t="b">
@@ -3368,11 +3372,11 @@
         <v>1</v>
       </c>
       <c r="B174" t="n">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>167_LH-AR-2021-e.pdf</t>
+          <t>128_2022-Q4-Report-EN.pdf</t>
         </is>
       </c>
       <c r="D174" t="b">
@@ -3382,31 +3386,35 @@
     </row>
     <row r="175">
       <c r="A175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B175" t="n">
-        <v>47</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>47_annual-report-2022.pdf</t>
-        </is>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="b">
-        <v>0</v>
-      </c>
-      <c r="E175" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://thewaltdisneycompany.com/app/uploads/2024/02/2023-Annual-Report.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B176" t="n">
-        <v>22</v>
-      </c>
-      <c r="C176" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>168_Aarsrapport_2023_engelsk_2024.pdf</t>
+        </is>
+      </c>
       <c r="D176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="inlineStr"/>
     </row>
@@ -3415,11 +3423,11 @@
         <v>1</v>
       </c>
       <c r="B177" t="n">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>103_Informe-anual-2024_ENG.pdf</t>
+          <t>148_diageo-annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D177" t="b">
@@ -3429,35 +3437,35 @@
     </row>
     <row r="178">
       <c r="A178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B178" t="n">
-        <v>265</v>
-      </c>
-      <c r="C178" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>13_2024ar.pdf</t>
+        </is>
+      </c>
       <c r="D178" t="b">
         <v>0</v>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.ssa.gov/forms/ssa-7050.pdf'</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="b">
         <v>1</v>
       </c>
       <c r="B179" t="n">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>244_Annual-CSR-Report-2023-24.pdf</t>
+          <t>266_aiy4w5teshy5t.pdf</t>
         </is>
       </c>
       <c r="D179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E179" t="inlineStr"/>
     </row>
@@ -3466,58 +3474,58 @@
         <v>1</v>
       </c>
       <c r="B180" t="n">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>126_agm-dsmfirmenich-integrated-annual-report-2023.pdf</t>
+          <t>86_BAT_Annual_Report_on_Form_20-F_2024.pdf</t>
         </is>
       </c>
       <c r="D180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B181" t="n">
-        <v>187</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>187_annualreport-2023.pdf</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="b">
         <v>0</v>
       </c>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Primary URL is not a valid PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B182" t="n">
-        <v>129</v>
-      </c>
-      <c r="C182" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>32_gabriel_annual_report_2022-23.pdf</t>
+        </is>
+      </c>
       <c r="D182" t="b">
         <v>0</v>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://corporate.mcdonalds.com/content/dam/sites/corp/nfl/pdf/McD%20-%202024%20Annual%20Report%20to%20Shareholders.pdf'</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="b">
         <v>0</v>
       </c>
       <c r="B183" t="n">
-        <v>90</v>
+        <v>247</v>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="b">
@@ -3525,7 +3533,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cannot connect to host annualreport2024.volkswagen-group.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1082)')]</t>
+          <t>Cannot connect to host ncert.nic.in:443 ssl:default [The specified network name is no longer available]</t>
         </is>
       </c>
     </row>
@@ -3534,11 +3542,11 @@
         <v>1</v>
       </c>
       <c r="B184" t="n">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>70_MunichRe-Group-Annual-Report-2024-en.pdf</t>
+          <t>208_ghg-protocol-revised.pdf</t>
         </is>
       </c>
       <c r="D184" t="b">
@@ -3548,82 +3556,82 @@
     </row>
     <row r="185">
       <c r="A185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B185" t="n">
-        <v>238</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>238_jpm-us-smaller-companies-web-hyr-2025.pdf</t>
-        </is>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="b">
         <v>0</v>
       </c>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://www.nomuraholdings.com/en/investor/library/sec/main/0112/teaserItems2/00/linkList/0/link/240412.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="b">
         <v>1</v>
       </c>
       <c r="B186" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>86_BAT_Annual_Report_on_Form_20-F_2024.pdf</t>
+          <t>111_adbe-2024-annual-report.pdf</t>
         </is>
       </c>
       <c r="D186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B187" t="n">
-        <v>207</v>
-      </c>
-      <c r="C187" t="inlineStr"/>
+        <v>129</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>129_McD%20-%202024%20Annual%20Report%20to%20Shareholders.pdf</t>
+        </is>
+      </c>
       <c r="D187" t="b">
         <v>0</v>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://cdn.rigsrevisionen.dk/rigsrevisionen/Media/638229369267919065/Annual-report-2022.pdf'</t>
-        </is>
-      </c>
+      <c r="E187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B188" t="n">
-        <v>71</v>
-      </c>
-      <c r="C188" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>72_fs_uk_year2020.pdf</t>
+        </is>
+      </c>
       <c r="D188" t="b">
-        <v>1</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.hul.co.in/files/hul-integrated-annual-report-2024-25.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="b">
         <v>1</v>
       </c>
       <c r="B189" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>168_Aarsrapport_2023_engelsk_2024.pdf</t>
+          <t>165_richemont-fy24-annual-report-en.pdf</t>
         </is>
       </c>
       <c r="D189" t="b">
@@ -3636,11 +3644,11 @@
         <v>1</v>
       </c>
       <c r="B190" t="n">
-        <v>226</v>
+        <v>110</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>226_240226-annual-report-and-accounts-2023.pdf</t>
+          <t>110_nykredit_q4_24_2025-02-05_en.pdf</t>
         </is>
       </c>
       <c r="D190" t="b">
@@ -3653,11 +3661,11 @@
         <v>1</v>
       </c>
       <c r="B191" t="n">
-        <v>31</v>
+        <v>267</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>31_tdc-net-annual-report-2023.pdf</t>
+          <t>267_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
         </is>
       </c>
       <c r="D191" t="b">
@@ -3670,11 +3678,11 @@
         <v>1</v>
       </c>
       <c r="B192" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>13_2024ar.pdf</t>
+          <t>47_annual-report-2022.pdf</t>
         </is>
       </c>
       <c r="D192" t="b">
@@ -3684,31 +3692,31 @@
     </row>
     <row r="193">
       <c r="A193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B193" t="n">
-        <v>266</v>
-      </c>
-      <c r="C193" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>33_annual-report-2023.pdf</t>
+        </is>
+      </c>
       <c r="D193" t="b">
-        <v>1</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.adobe.com/cc-shared/assets/investor-relations/pdfs/11905202/aiy4w5teshy5t.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="b">
         <v>1</v>
       </c>
       <c r="B194" t="n">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>206_full-report.pdf</t>
+          <t>150_annual-reports-one-pager.pdf</t>
         </is>
       </c>
       <c r="D194" t="b">
@@ -3718,35 +3726,35 @@
     </row>
     <row r="195">
       <c r="A195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B195" t="n">
-        <v>91</v>
-      </c>
-      <c r="C195" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>9_carlsberg-breweries-group_2024-annual-report.pdf</t>
+        </is>
+      </c>
       <c r="D195" t="b">
-        <v>0</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Primary URL is not a valid PDF.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="b">
         <v>1</v>
       </c>
       <c r="B196" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>9_carlsberg-breweries-group_2024-annual-report.pdf</t>
+          <t>50_Annual-Report-2023.pdf</t>
         </is>
       </c>
       <c r="D196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196" t="inlineStr"/>
     </row>
@@ -3755,15 +3763,15 @@
         <v>1</v>
       </c>
       <c r="B197" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>11_annual-report-adidas-ar24.pdf</t>
+          <t>52_Kingfisher-Annual-Report-2024-25.pdf</t>
         </is>
       </c>
       <c r="D197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E197" t="inlineStr"/>
     </row>
@@ -3772,11 +3780,11 @@
         <v>1</v>
       </c>
       <c r="B198" t="n">
-        <v>12</v>
+        <v>245</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>12_annual-report-2024.pdf</t>
+          <t>245_The-Sustainable-Development-Goals-Report-2025.pdf</t>
         </is>
       </c>
       <c r="D198" t="b">
@@ -3786,31 +3794,31 @@
     </row>
     <row r="199">
       <c r="A199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B199" t="n">
-        <v>247</v>
-      </c>
-      <c r="C199" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>34_10-Q4-2024-As-Filed.pdf</t>
+        </is>
+      </c>
       <c r="D199" t="b">
         <v>0</v>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Cannot connect to host ncert.nic.in:443 ssl:default [The specified network name is no longer available]</t>
-        </is>
-      </c>
+      <c r="E199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="b">
         <v>1</v>
       </c>
       <c r="B200" t="n">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>148_diageo-annual-report-2024.pdf</t>
+          <t>188_bn_annual_report_2023.pdf</t>
         </is>
       </c>
       <c r="D200" t="b">
@@ -3820,31 +3828,31 @@
     </row>
     <row r="201">
       <c r="A201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B201" t="n">
-        <v>111</v>
-      </c>
-      <c r="C201" t="inlineStr"/>
+        <v>248</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>248_Macfarlane-Group-PLC-Interim-Report-2025.pdf</t>
+        </is>
+      </c>
       <c r="D201" t="b">
         <v>0</v>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.adobe.com/cc-shared/assets/investor-relations/pdfs/adbe-2024-annual-report.pdf'</t>
-        </is>
-      </c>
+      <c r="E201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="b">
         <v>1</v>
       </c>
       <c r="B202" t="n">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>110_nykredit_q4_24_2025-02-05_en.pdf</t>
+          <t>228_Fundamentals-to-Best-Practices-Slides.pdf</t>
         </is>
       </c>
       <c r="D202" t="b">
@@ -3854,27 +3862,27 @@
     </row>
     <row r="203">
       <c r="A203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B203" t="n">
-        <v>169</v>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>169_FS_Group_2023_Annual_Report.pdf</t>
-        </is>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="b">
         <v>0</v>
       </c>
-      <c r="E203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://www.parliament.uk/globalassets/documents/commons-expenditure/admin-annual-accounts/administration_annual_report_and_accounts_2022_23-accessible.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="b">
         <v>0</v>
       </c>
       <c r="B204" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="b">
@@ -3882,7 +3890,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.michigan.gov/treasury/-/media/Project/Websites/treasury/BLGSS/LAFD/Webinar/FY25/Fundamentals-to-Best-Practices-Slides.pdf'</t>
+          <t>404, message='Not Found', url='https://www.eif.org/files/records/eif-annual-report-2021.pdf'</t>
         </is>
       </c>
     </row>
@@ -3891,11 +3899,11 @@
         <v>1</v>
       </c>
       <c r="B205" t="n">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>227_2023-Annual-Report.pdf</t>
+          <t>189_0001193125-24-092555.pdf</t>
         </is>
       </c>
       <c r="D205" t="b">
@@ -3908,11 +3916,11 @@
         <v>1</v>
       </c>
       <c r="B206" t="n">
-        <v>267</v>
+        <v>190</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>267_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
+          <t>190_RMTF_2024-25_FINAL.pdf</t>
         </is>
       </c>
       <c r="D206" t="b">
@@ -3925,11 +3933,11 @@
         <v>1</v>
       </c>
       <c r="B207" t="n">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>150_annual-reports-one-pager.pdf</t>
+          <t>268_budget_speech.pdf</t>
         </is>
       </c>
       <c r="D207" t="b">
@@ -3939,65 +3947,65 @@
     </row>
     <row r="208">
       <c r="A208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B208" t="n">
-        <v>72</v>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>72_fs_uk_year2020.pdf</t>
-        </is>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="b">
         <v>0</v>
       </c>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://www.economie.gouv.fr/files/files/directions_services/agence-participations-etat/Documents/Rapports-de-l-Etat-actionnaire/2023/REA2023_Ang-web.pdf?v=1705416463'</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B209" t="n">
-        <v>130</v>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>130_240412.pdf</t>
-        </is>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="b">
         <v>0</v>
       </c>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Primary URL is not a valid PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B210" t="n">
-        <v>170</v>
-      </c>
-      <c r="C210" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>92_SPAR_IAR_2024.pdf</t>
+        </is>
+      </c>
       <c r="D210" t="b">
         <v>0</v>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.pwc.se/sv/om-oss/annual-report-2023-2024.pdf'</t>
-        </is>
-      </c>
+      <c r="E210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="b">
         <v>1</v>
       </c>
       <c r="B211" t="n">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>208_ghg-protocol-revised.pdf</t>
+          <t>73_annual-report-2024-e.pdf</t>
         </is>
       </c>
       <c r="D211" t="b">
@@ -4010,15 +4018,15 @@
         <v>1</v>
       </c>
       <c r="B212" t="n">
-        <v>14</v>
+        <v>246</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>14_richemont-fy25-annual-report-en.pdf</t>
+          <t>246_SDG_India_Index_2023-24.pdf</t>
         </is>
       </c>
       <c r="D212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E212" t="inlineStr"/>
     </row>
@@ -4027,11 +4035,11 @@
         <v>1</v>
       </c>
       <c r="B213" t="n">
-        <v>34</v>
+        <v>249</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>34_10-Q4-2024-As-Filed.pdf</t>
+          <t>249_InvestorDay2025.pdf</t>
         </is>
       </c>
       <c r="D213" t="b">
@@ -4044,15 +4052,15 @@
         <v>1</v>
       </c>
       <c r="B214" t="n">
-        <v>248</v>
+        <v>71</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>248_Macfarlane-Group-PLC-Interim-Report-2025.pdf</t>
+          <t>71_hul-integrated-annual-report-2024-25.pdf</t>
         </is>
       </c>
       <c r="D214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E214" t="inlineStr"/>
     </row>
@@ -4061,11 +4069,11 @@
         <v>1</v>
       </c>
       <c r="B215" t="n">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>33_annual-report-2023.pdf</t>
+          <t>170_annual-report-2023-2024.pdf</t>
         </is>
       </c>
       <c r="D215" t="b">
@@ -4078,15 +4086,15 @@
         <v>1</v>
       </c>
       <c r="B216" t="n">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>245_The-Sustainable-Development-Goals-Report-2025.pdf</t>
+          <t>209_94fcfb43-c9be-4d9a-8d43-2fa983be69fa.pdf</t>
         </is>
       </c>
       <c r="D216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E216" t="inlineStr"/>
     </row>
@@ -4095,45 +4103,45 @@
         <v>1</v>
       </c>
       <c r="B217" t="n">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>52_Kingfisher-Annual-Report-2024-25.pdf</t>
+          <t>169_FS_Group_2023_Annual_Report.pdf</t>
         </is>
       </c>
       <c r="D217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B218" t="n">
-        <v>229</v>
-      </c>
-      <c r="C218" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>74_LH-AR-2024-e.pdf</t>
+        </is>
+      </c>
       <c r="D218" t="b">
         <v>0</v>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>404, message='Not Found', url='https://www.eif.org/files/records/eif-annual-report-2021.pdf'</t>
-        </is>
-      </c>
+      <c r="E218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="b">
         <v>1</v>
       </c>
       <c r="B219" t="n">
-        <v>188</v>
+        <v>53</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>188_bn_annual_report_2023.pdf</t>
+          <t>53_puma-annual-report-2024-en-final.pdf</t>
         </is>
       </c>
       <c r="D219" t="b">
@@ -4146,11 +4154,11 @@
         <v>1</v>
       </c>
       <c r="B220" t="n">
-        <v>268</v>
+        <v>152</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>268_budget_speech.pdf</t>
+          <t>152_Ryanair-2019-Annual-Report.pdf</t>
         </is>
       </c>
       <c r="D220" t="b">
@@ -4160,35 +4168,35 @@
     </row>
     <row r="221">
       <c r="A221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B221" t="n">
-        <v>190</v>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>190_RMTF_2024-25_FINAL.pdf</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C221" t="inlineStr"/>
       <c r="D221" t="b">
         <v>0</v>
       </c>
-      <c r="E221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.ey.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="b">
         <v>1</v>
       </c>
       <c r="B222" t="n">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>112_administration_annual_report_and_accounts_2022_23-accessible.pdf</t>
+          <t>35_Barclays-PLC-Annual-Report-2024.pdf</t>
         </is>
       </c>
       <c r="D222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E222" t="inlineStr"/>
     </row>
@@ -4197,15 +4205,15 @@
         <v>1</v>
       </c>
       <c r="B223" t="n">
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>209_94fcfb43-c9be-4d9a-8d43-2fa983be69fa.pdf</t>
+          <t>126_agm-dsmfirmenich-integrated-annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E223" t="inlineStr"/>
     </row>
@@ -4214,11 +4222,11 @@
         <v>1</v>
       </c>
       <c r="B224" t="n">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>53_puma-annual-report-2024-en-final.pdf</t>
+          <t>133_2023-annual-report-storbrand-asa.pdf</t>
         </is>
       </c>
       <c r="D224" t="b">
@@ -4231,11 +4239,11 @@
         <v>1</v>
       </c>
       <c r="B225" t="n">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>132_REA2023_Ang-web.pdf</t>
+          <t>94_bsc-2024-annual-report-and-10-k.pdf</t>
         </is>
       </c>
       <c r="D225" t="b">
@@ -4245,48 +4253,44 @@
     </row>
     <row r="226">
       <c r="A226" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B226" t="n">
-        <v>189</v>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>189_0001193125-24-092555.pdf</t>
-        </is>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="C226" t="inlineStr"/>
       <c r="D226" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B227" t="n">
-        <v>171</v>
-      </c>
-      <c r="C227" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>36_eu-16677_semi_annual_report_f_0.pdf</t>
+        </is>
+      </c>
       <c r="D227" t="b">
         <v>0</v>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Primary URL is not a valid PDF.</t>
-        </is>
-      </c>
+      <c r="E227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="b">
         <v>1</v>
       </c>
       <c r="B228" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>249_InvestorDay2025.pdf</t>
+          <t>250_250916---Notice-of-Annual-General-Meeting-2025.pdf</t>
         </is>
       </c>
       <c r="D228" t="b">
@@ -4296,31 +4300,31 @@
     </row>
     <row r="229">
       <c r="A229" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B229" t="n">
-        <v>50</v>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>50_Annual-Report-2023.pdf</t>
-        </is>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C229" t="inlineStr"/>
       <c r="D229" t="b">
         <v>0</v>
       </c>
-      <c r="E229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://www.fma.govt.nz/assets/Reports/KiwiSaver-Annual-Report-2025.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="b">
         <v>1</v>
       </c>
       <c r="B230" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>15_E_2024%20Annual%20Report.pdf</t>
+          <t>16_annual_report2024.pdf</t>
         </is>
       </c>
       <c r="D230" t="b">
@@ -4330,31 +4334,31 @@
     </row>
     <row r="231">
       <c r="A231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B231" t="n">
-        <v>113</v>
-      </c>
-      <c r="C231" t="inlineStr"/>
+        <v>210</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>210_Cleveland_Public_Library_2024_Cuyahoga_FINAL.pdf</t>
+        </is>
+      </c>
       <c r="D231" t="b">
-        <v>1</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.bhp.com/-/media/documents/investors/annual-reports/2019/bhpannualreport2019.pdf'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="b">
         <v>1</v>
       </c>
       <c r="B232" t="n">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>74_LH-AR-2024-e.pdf</t>
+          <t>192_PDJF_Aarsrapport_2023_Signed.pdf</t>
         </is>
       </c>
       <c r="D232" t="b">
@@ -4367,15 +4371,15 @@
         <v>1</v>
       </c>
       <c r="B233" t="n">
-        <v>32</v>
+        <v>270</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>32_gabriel_annual_report_2022-23.pdf</t>
+          <t>270_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
         </is>
       </c>
       <c r="D233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233" t="inlineStr"/>
     </row>
@@ -4398,31 +4402,31 @@
     </row>
     <row r="235">
       <c r="A235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B235" t="n">
-        <v>55</v>
-      </c>
-      <c r="C235" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>14_richemont-fy25-annual-report-en.pdf</t>
+        </is>
+      </c>
       <c r="D235" t="b">
-        <v>0</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.ey.com:443 ssl:True [SSLCertVerificationError: (1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1082)')]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="b">
         <v>1</v>
       </c>
       <c r="B236" t="n">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>210_Cleveland_Public_Library_2024_Cuyahoga_FINAL.pdf</t>
+          <t>191_diluen_annualreport_2023_sicav.pdf</t>
         </is>
       </c>
       <c r="D236" t="b">
@@ -4435,11 +4439,11 @@
         <v>1</v>
       </c>
       <c r="B237" t="n">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>152_Ryanair-2019-Annual-Report.pdf</t>
+          <t>114_ABENA-Annual-Report-2023-2024_EN.pdf</t>
         </is>
       </c>
       <c r="D237" t="b">
@@ -4449,31 +4453,31 @@
     </row>
     <row r="238">
       <c r="A238" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B238" t="n">
-        <v>94</v>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>94_bsc-2024-annual-report-and-10-k.pdf</t>
-        </is>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C238" t="inlineStr"/>
       <c r="D238" t="b">
-        <v>0</v>
-      </c>
-      <c r="E238" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.bertelsmannn.com:443 ssl:default [[SSL: TLSV1_ALERT_INTERNAL_ERROR] tlsv1 alert internal error (_ssl.c:1082)]</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="b">
         <v>1</v>
       </c>
       <c r="B239" t="n">
-        <v>16</v>
+        <v>251</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>16_annual_report2024.pdf</t>
+          <t>251_Draft%20conclusions_2nd%20BTR%20LRs%20meeting_2025.pdf</t>
         </is>
       </c>
       <c r="D239" t="b">
@@ -4486,11 +4490,11 @@
         <v>1</v>
       </c>
       <c r="B240" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>73_annual-report-2024-e.pdf</t>
+          <t>56_VSO%20Annual%20Report%202011-12.pdf</t>
         </is>
       </c>
       <c r="D240" t="b">
@@ -4500,35 +4504,35 @@
     </row>
     <row r="241">
       <c r="A241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B241" t="n">
-        <v>131</v>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>131_Consolidated-Annual-Accounts-2023.pdf</t>
-        </is>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C241" t="inlineStr"/>
       <c r="D241" t="b">
-        <v>1</v>
-      </c>
-      <c r="E241" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>400, message='Can not decode content-encoding: brotli (br). Please install `Brotli`', url='https://cdnmedia.eurofins.com/corporate-eurofins/media/wmvnjc2u/eurofins-scientific-2024-annual-report.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="b">
         <v>1</v>
       </c>
       <c r="B242" t="n">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>36_eu-16677_semi_annual_report_f_0.pdf</t>
+          <t>113_bhpannualreport2019.pdf</t>
         </is>
       </c>
       <c r="D242" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E242" t="inlineStr"/>
     </row>
@@ -4537,28 +4541,24 @@
         <v>0</v>
       </c>
       <c r="B243" t="n">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="b">
-        <v>0</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>403, message='Forbidden', url='https://www.fma.govt.nz/assets/Reports/KiwiSaver-Annual-Report-2025.pdf'</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="b">
         <v>1</v>
       </c>
       <c r="B244" t="n">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>92_SPAR_IAR_2024.pdf</t>
+          <t>37_grantthornton_annual-report_2023_uk.pdf</t>
         </is>
       </c>
       <c r="D244" t="b">
@@ -4571,15 +4571,15 @@
         <v>0</v>
       </c>
       <c r="B245" t="n">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>403, message='Forbidden', url='https://www.tesla.com/sites/default/files/downloads/TSLA-Q2-2025-Update.pdf'</t>
+          <t>Secondary URL is not a valid PDF.</t>
         </is>
       </c>
     </row>
@@ -4588,15 +4588,15 @@
         <v>1</v>
       </c>
       <c r="B246" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>270_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
+          <t>271_ac099961-fbfb-418d-852e-303e567600e1.pdf</t>
         </is>
       </c>
       <c r="D246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246" t="inlineStr"/>
     </row>
@@ -4605,11 +4605,11 @@
         <v>1</v>
       </c>
       <c r="B247" t="n">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>250_250916---Notice-of-Annual-General-Meeting-2025.pdf</t>
+          <t>115_aarsregnskab_2019_engelsk_2020_ok.pdf</t>
         </is>
       </c>
       <c r="D247" t="b">
@@ -4619,31 +4619,31 @@
     </row>
     <row r="248">
       <c r="A248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B248" t="n">
-        <v>246</v>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>246_SDG_India_Index_2023-24.pdf</t>
-        </is>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="C248" t="inlineStr"/>
       <c r="D248" t="b">
-        <v>0</v>
-      </c>
-      <c r="E248" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Cannot connect to host www.pepsino.com:443 ssl:default [None]</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="b">
         <v>1</v>
       </c>
       <c r="B249" t="n">
-        <v>35</v>
+        <v>173</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>35_Barclays-PLC-Annual-Report-2024.pdf</t>
+          <t>173_kerry-group-annual-report-2023.pdf</t>
         </is>
       </c>
       <c r="D249" t="b">
@@ -4653,14 +4653,18 @@
     </row>
     <row r="250">
       <c r="A250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B250" t="n">
-        <v>241</v>
-      </c>
-      <c r="C250" t="inlineStr"/>
+        <v>232</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>232_OSHA-RK-Forms-Package.pdf</t>
+        </is>
+      </c>
       <c r="D250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E250" t="inlineStr"/>
     </row>
@@ -4669,11 +4673,11 @@
         <v>1</v>
       </c>
       <c r="B251" t="n">
-        <v>114</v>
+        <v>231</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>114_ABENA-Annual-Report-2023-2024_EN.pdf</t>
+          <t>231_TSLA-Q2-2025-Update.pdf</t>
         </is>
       </c>
       <c r="D251" t="b">
@@ -4683,31 +4687,31 @@
     </row>
     <row r="252">
       <c r="A252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B252" t="n">
-        <v>192</v>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>192_PDJF_Aarsrapport_2023_Signed.pdf</t>
-        </is>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C252" t="inlineStr"/>
       <c r="D252" t="b">
         <v>0</v>
       </c>
-      <c r="E252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>404, message='Not Found', url='https://pka.dk/globalassets/4-this-is-pka/annual-report/2023/annual-report-2023-pka-pension.pdf'</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="b">
         <v>1</v>
       </c>
       <c r="B253" t="n">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>251_Draft%20conclusions_2nd%20BTR%20LRs%20meeting_2025.pdf</t>
+          <t>154_MILITARY-AND-SECURITY-DEVELOPMENTS-INVOLVING-THE-PEOPLES-REPUBLIC-OF-CHINA-PLEASE-HELP-CAPS-LOCK-STUCK-2024.pdf</t>
         </is>
       </c>
       <c r="D253" t="b">
@@ -4717,48 +4721,44 @@
     </row>
     <row r="254">
       <c r="A254" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B254" t="n">
-        <v>191</v>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>191_diluen_annualreport_2023_sicav.pdf</t>
-        </is>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C254" t="inlineStr"/>
       <c r="D254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B255" t="n">
-        <v>134</v>
-      </c>
-      <c r="C255" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>15_E_2024%20Annual%20Report.pdf</t>
+        </is>
+      </c>
       <c r="D255" t="b">
-        <v>1</v>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.bertelsmannn.com:443 ssl:default [[SSL: TLSV1_ALERT_INTERNAL_ERROR] tlsv1 alert internal error (_ssl.c:1082)]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="b">
         <v>1</v>
       </c>
       <c r="B256" t="n">
-        <v>56</v>
+        <v>252</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>56_VSO%20Annual%20Report%202011-12.pdf</t>
+          <t>252_cpi.pdf</t>
         </is>
       </c>
       <c r="D256" t="b">
@@ -4771,45 +4771,45 @@
         <v>1</v>
       </c>
       <c r="B257" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>17_novo-nordisk-annual-report-2023.pdf</t>
+          <t>57_annual-report-2024.pdf</t>
         </is>
       </c>
       <c r="D257" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B258" t="n">
-        <v>212</v>
-      </c>
-      <c r="C258" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>96_ecit-annual-report-2023-62971.pdf</t>
+        </is>
+      </c>
       <c r="D258" t="b">
-        <v>1</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>Cannot connect to host www.pepsino.com:443 ssl:default [None]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="b">
         <v>1</v>
       </c>
       <c r="B259" t="n">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>95_niras_annual-report_2023.pdf</t>
+          <t>172_aa-annual-report-full-2021.pdf</t>
         </is>
       </c>
       <c r="D259" t="b">
@@ -4822,39 +4822,47 @@
         <v>1</v>
       </c>
       <c r="B260" t="n">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>172_aa-annual-report-full-2021.pdf</t>
+          <t>93_2024-Annual_Report.pdf</t>
         </is>
       </c>
       <c r="D260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B261" t="n">
-        <v>28</v>
-      </c>
-      <c r="C261" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>95_niras_annual-report_2023.pdf</t>
+        </is>
+      </c>
       <c r="D261" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B262" t="n">
-        <v>67</v>
-      </c>
-      <c r="C262" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>17_novo-nordisk-annual-report-2023.pdf</t>
+        </is>
+      </c>
       <c r="D262" t="b">
         <v>0</v>
       </c>
@@ -4865,11 +4873,11 @@
         <v>1</v>
       </c>
       <c r="B263" t="n">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>133_2023-annual-report-storbrand-asa.pdf</t>
+          <t>174_Bank-of-Ghana-2023-Annual-Report-and-Financial-Statements.pdf</t>
         </is>
       </c>
       <c r="D263" t="b">
@@ -4882,11 +4890,11 @@
         <v>1</v>
       </c>
       <c r="B264" t="n">
-        <v>211</v>
+        <v>135</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>211_annual-report-adidas-ar23.pdf</t>
+          <t>135_currys-annual-report-2023-24-web.pdf</t>
         </is>
       </c>
       <c r="D264" t="b">
@@ -4899,11 +4907,11 @@
         <v>1</v>
       </c>
       <c r="B265" t="n">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>173_kerry-group-annual-report-2023.pdf</t>
+          <t>269_the-state-of-organizations-2023.pdf</t>
         </is>
       </c>
       <c r="D265" t="b">
@@ -4933,11 +4941,11 @@
         <v>1</v>
       </c>
       <c r="B267" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>93_2024-Annual_Report.pdf</t>
+          <t>131_Consolidated-Annual-Accounts-2023.pdf</t>
         </is>
       </c>
       <c r="D267" t="b">
@@ -4947,14 +4955,18 @@
     </row>
     <row r="268">
       <c r="A268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B268" t="n">
-        <v>223</v>
-      </c>
-      <c r="C268" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>18_annual_report_2024_en.pdf</t>
+        </is>
+      </c>
       <c r="D268" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E268" t="inlineStr"/>
     </row>
@@ -4963,11 +4975,11 @@
         <v>1</v>
       </c>
       <c r="B269" t="n">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>230_amNsb3VkczovLzAzLzg2LzU1LzNhL2E2L2FhNDQtNDIyNi05MTFmLTQxYzdkYTU3ZTFmOQ.pdf</t>
+          <t>211_annual-report-adidas-ar23.pdf</t>
         </is>
       </c>
       <c r="D269" t="b">
@@ -4980,26 +4992,30 @@
         <v>1</v>
       </c>
       <c r="B270" t="n">
-        <v>149</v>
+        <v>230</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>149_ia-2020-annual-report-en.pdf</t>
+          <t>230_amNsb3VkczovLzAzLzg2LzU1LzNhL2E2L2FhNDQtNDIyNi05MTFmLTQxYzdkYTU3ZTFmOQ.pdf</t>
         </is>
       </c>
       <c r="D270" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B271" t="n">
-        <v>51</v>
-      </c>
-      <c r="C271" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>149_ia-2020-annual-report-en.pdf</t>
+        </is>
+      </c>
       <c r="D271" t="b">
         <v>1</v>
       </c>
@@ -5010,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="n">
-        <v>269</v>
+        <v>51</v>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="b">
